--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,70 +444,75 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>lawful_basis</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>send_attempts</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>message_id</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>last_error</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>date_added</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>date_contacted</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>meeting_status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>meeting_time</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>proposed_slots_json</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>meeting_notes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>meeting_updated</t>
         </is>
@@ -531,58 +536,59 @@
           <t>https://zankore.com</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>web_research: https://zankore.com/ — Indosat, Ooredoo Group, Nokia and Nvidia launched Zankore, targeting 1GW of Nvidia DSX AI Factory capacity in Indonesia, with an initial ~200MW live in Jakarta by H1 2027</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>gmail:1a073bddc5d568b3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,58 +612,59 @@
           <t>https://dci-indonesia.com</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>web_research: https://dci-indonesia.com/news/dci-indonesia-inaugurates-e2-surabaya-expanding-its-platform-to-eastern-indonesia — Inaugurated E2 Surabaya (9MW IT load), its first data center in Eastern Indonesia, and separately raised a $980M loan to fund AI-era capacity expansion</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>gmail:1a073bd4a311c874</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,58 +692,59 @@
           <t>https://digitaledgedc.com</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>web_research: https://www.digitaledgedc.com/resources/newsroom/digital-edge-4-5b-cgk-500mw-ai-ready-hyperscale-campus-indonesia/ — Announced a $4.5B investment in CGK Campus, a 500MW (scaling to 1GW) AI-ready hyperscale data center in Bekasi featuring direct-to-chip liquid cooling and a 1.25 target PUE</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>gmail:1a073be6a2869476</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -760,58 +768,59 @@
           <t>https://neutradc.com</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>web_research: https://www.neutradc.com/news/60643/data-center-fully-secured-before-launch-telkom-indonesia-accelerates-expansion-of-neutradc-capacity-in-batam — Accelerating NeutraDC AI data center capacity in Batam (Nxera, 18MW initial phase scaling to 54MW) plus a 200MW Cikarang hyperscale expansion secured via a PLN power deal</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>gmail:1a073bd609a9863d</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -831,58 +840,59 @@
           <t>https://bdxworld.com</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>web_research: https://www.bdxworld.com/locations/indonesia/ — Building BDx Jakarta CGK3, one of Indonesia's first liquid-cooled AI data center campuses, plus a $320M loan-backed expansion of CGK4/CGK5 to 1.2GVA for high-density AI workloads</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>gmail:1a073bdf45fcb5c0</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -902,58 +912,59 @@
           <t>https://firmus.co</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>web_research: https://firmus.co/newsroom/firmus-to-build-170-000-gpu-ai-factor-y-campus-with-nvidia-for-global-ai-natives — Partnering with Nvidia on an 8-year deal to build a 360MW, 170,000-GPU AI Factory campus in Batam, Indonesia, going live Q1 2027</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>gmail:1a073be85a254b4e</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -977,58 +988,59 @@
           <t>https://brin.go.id</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>web_research: https://www.brin.go.id/en/news/122525/indonesia-and-korea-launch-hpc-supercomputer-encourage-asean-digital-collaboration — BRIN launched a Top500-ranked HPC supercomputer facility (MAHAMERU) with South Korea under the ASEAN-Korea Digital Innovation Flagship, accelerating scientific data processing from 10 hours to 10 seconds -- a compute density that requires serious thermal management</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>gmail:1a074b3d7bd7faf0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1052,58 +1064,59 @@
           <t>https://www.gawcapital.com</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>web_research: https://www.gawcapital.com/news/pressrelease/gaw-capital-partners-announces-the-launch-of-golden-digital-gateway-data-center-in-nongsa-digital-park-indonesia/ — Launched Golden Digital Gateway, a carrier-neutral colocation data center JV with Sinar Primera in Nongsa Digital Park, Batam -- 5.2MW first phase live, with a second phase planned to expand to 20MW</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>gmail:1a074b5557022ca6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1127,58 +1140,59 @@
           <t>https://ionnetwork.co.id</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>web_research: https://blog.ionnetwork.co.id/ion-network-resmikan-prodc-data-center-bali-perkuat-infrastruktur-digital-indonesia-timur/ — Officially launched ProDC Data Center Bali and a new Denpasar regional office on 25 June 2026 to strengthen digital infrastructure in Eastern Indonesia, with plans to build a further data center in Semarang</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>gmail:1a074b44f85d0c6a</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1202,58 +1216,59 @@
           <t>https://biznetdatacenter.com</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>web_research: https://www.inilah.com/biznet-bangun-ai-data-center-pertama-di-bali-target-rampung-oktober-2025 — Building Indonesia's first AI-Ready Data Center in Jimbaran, Bali (Karang Mas Estate), targeted for completion October 2025, positioned as a high-capacity AI processing hub and AI technology development lab</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>gmail:1a074b3ecc4ed0a2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1277,58 +1292,59 @@
           <t>https://omadata.com</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>web_research: https://www.antaranews.com/berita/5435506/omadata-hadir-di-makassar-guna-perkuat-infrastruktur-digital — Officially expanding into Makassar with a new E3 Data Center at CitraLand City CPI to serve as an eastern-Indonesia edge hub for the ~100 ISPs in the Sulampua region needing low-latency, high-reliability capacity</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>gmail:1a074b497e7836c4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1352,58 +1368,59 @@
           <t>https://rackscentral.com</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>web_research: https://www.rackscentral.com/news/racks-central-expands-footprint-with-new-land-acquisition-in-nongsa-digital-park-batam — Building a 95MW greenfield campus in Nongsa Digital Park, Batam, purpose-built for high-density compute and AI workloads with liquid-ready cooling and high rack power densities, backed by a $1B China-ASEAN investment fund commitment</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>gmail:1a074b4eb92f9e82</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1427,58 +1444,59 @@
           <t>https://aws.amazon.com</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>web_research: https://www.amazon.jobs/en/jobs/3187721/dceo-facility-manager-indonesia-data-center-engineering-operations — Actively hiring a DCEO Facility Manager for its Indonesia data center cluster to manage electrical/mechanical critical infrastructure (chillers, cooling towers, CRAH units, generators, UPS) supporting the AWS Asia Pacific (Jakarta) Region</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>1a0812521f679104</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:32+00:00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1502,58 +1520,59 @@
           <t>https://ugm.ac.id</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>web_research: https://ugm.ac.id/en/news/ugm-partners-with-nvidia-and-indosat-to-advance-ai-research/ — Hosting the UGM Indosat NVIDIA AI Technology Center (opened August 2026), Indonesia's first university AI center, with an NVIDIA DGX Station AI supercomputer placed at the Faculty of Engineering and Faculty of Mathematics and Natural Sciences</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>1a08124e1a4af6af</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:15+00:00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1581,58 +1600,59 @@
           <t>https://datacomm.co.id</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>web_research: https://www.prnewswire.com/news-releases/nokia-blaize-and-datacomm-diangraha-unite-to-deliver-hybrid-ai-inference-across-indonesia-and-southeast-asia-302755505.html — Announced (April 2026) a strategic alliance with Nokia and Blaize to deploy hybrid AI inference infrastructure across Indonesia, with Datacomm's own leadership stating data centers must evolve toward GPU infrastructure to meet enterprise/public-sector AI demand</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>1a0812444a22266b</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:36+00:00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1656,58 +1676,59 @@
           <t>https://nexdatacenter.com</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>web_research: https://www.nexdatacenter.com/locations/ — Operates multiple Tier III colocation facilities in Jakarta CBD (Cyber 2 Tower, Menara Tendean) purpose-built for high-density deployments up to 10kVA per rack, part of Indonesia's growing carrier-neutral colocation cluster</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>1a081250146ef7f5</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:24+00:00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1731,58 +1752,59 @@
           <t>https://spacedc.com</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>web_research: https://spacedc.com/spacedcs-data-center-campus-first-in-indonesia-to-feature-advanced-cooling-technology-to-facilitate-energy-and-space-efficiencies/ — JAK1 Jakarta campus is first in Indonesia to feature advanced cooling technology (Vertiv thermal walls, N+1 high-efficiency air-cooled chillers with cogeneration absorption chillers, hot-aisle containment) with water-cooled racks up to 50kW each</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>1a08124bed10cf44</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:07+00:00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1810,58 +1832,59 @@
           <t>https://equinix.com</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>web_research: https://newsroom.equinix.com/2025-05-15-Equinix-Unveils-Its-First-AI-Ready-Data-Center-with-Dense-Ecosystem-in-Jakarta — Inaugurated JK1, its first AI-ready IBX data center in Jakarta (JV with PT Astra International), with phase two adding liquid cooling and Cooling Array technology to support higher-density AI workloads at a target PUE of 1.41</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>1a0812481201f6c1</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:51+00:00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1885,58 +1908,59 @@
           <t>https://area31.id</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/area31-to-invest-675m-in-depok-indonesia-data-center/ — Committing ~$67.5M over five years to expand its Depok (Cimanggis) hyperscale campus, including a new Data Hall 2 (150+ racks, 600kW capacity) at its AI-ready, carrier-neutral RATED 3 facility</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>1a08124a14825778</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:59+00:00</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1960,58 +1984,59 @@
           <t>https://biznetgio.com</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>web_research: https://www.biznetgio.com/en/product/neo-gpu — Launched NEO GPU cloud service offering up to 8x NVIDIA H200 GPUs per instance (3,958 TFLOPS, 1,128GB HBM3e with NVLink) for AI training/inference workloads hosted in its Indonesia data centers</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>1a08124631a7bea9</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:43+00:00</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2035,58 +2060,59 @@
           <t>https://wowrack.co.id</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>web_research: https://www.wowrack.com/en-us/blog/colocation/gpu-as-a-service/ — Offers GPU-as-a-Service (GPUaaS) out of its Jakarta and Surabaya data centers, giving AI teams on-demand access to GPU capacity without their own hardware investment, amid rising Indonesian AI/GPU infrastructure demand</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>1a0812564d07ef3e</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:50+00:00</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2110,58 +2136,59 @@
           <t>https://zettagrid.id</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>web_research: https://www.zettagrid.id/gpu-vworkstations/ — Offers Enterprise AI Instances powered by Dell servers with NVIDIA A100 and H100 GPUs, plus GPU vWorkstations, run on VMware infrastructure with NVIDIA AI Enterprise in its Indonesia data center</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>1a0812541647810f</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:40+00:00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2181,58 +2208,59 @@
           <t>https://peruri.co.id</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>web_research: https://www.lintasarta.net/en/news/lintasarta-presents-gpu-merdeka-an-advanced-sovereign-ai-cloud-for-indonesia-powered-by-nvidia-ai/ — Peruri's Digital Business Director Farah Fitria Rahmayanti participated in the launch of GPU Merdeka, Indonesia's NVIDIA-powered sovereign AI GPU-as-a-Service cloud, indicating Peruri is adopting GPU-accelerated AI infrastructure for its state digital security services</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>1a0850fb72832e3a</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:38+00:00</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2252,58 +2280,59 @@
           <t>https://telin.net</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/telin-and-bw-digital-partner-on-batam-singapore-subsea-cable/ — Telin is building the new Nongsa-Changi Cable and INSICA subsea cable systems (landed Jul 2026 / ready Q4 2026) specifically to carry the surge in data-center-to-data-center traffic between Batam and Singapore, signaling major new DC interconnection capacity build-out</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>1a0850fd78650da2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:45+00:00</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2323,58 +2352,59 @@
           <t>https://ioh.co.id</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>web_research: https://blogs.nvidia.com/blog/indonesia-ai-center-of-excellence — Building Indonesia's AI Center of Excellence with NVIDIA (Blackwell GPUs, NVIDIA Cloud Partner reference architectures) and Cisco (announced July 2025); also invested ~$200M in a Surakarta AI data center with NVIDIA and formed the Raia Grid JV to assemble NVIDIA GPUs domestically in Indonesia starting Dec 2026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>1a0850f96f15772b</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:30+00:00</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2394,58 +2424,59 @@
           <t>https://gds-services.com</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/gds-partners-with-indonesias-sovereign-wealth-fund-for-batam-data-center-campus/ — GDS Holdings and Indonesia's sovereign wealth fund (INA) formed a JV building a 28MW hyperscale data center campus at Nongsa Digital Park, Batam, integrating GDS's Smart DC solution</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>1a0850ff74446503</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:54+00:00</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2469,58 +2500,59 @@
           <t>https://intiland.com</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>web_research: https://ekonomi.bisnis.com/read/20260206/47/1950875/intiland-dild-luncurkan-data-center-land-di-surabaya-berkapasitas-3mw — Intiland (via JV PT Inti Arunika Persada with ION Network) launched DC Land data center at Intiland Tower Surabaya Feb 2026, live at 3MW with ~50% capacity already occupied, targeting expansion to 30MW to serve East Indonesia demand.</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>1a08a33a21b90f3b</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:50+00:00</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:58+00:00</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2544,58 +2576,59 @@
           <t>https://napinfo.co.id</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>web_research: https://napinfo.co.id/highlights/article/id/matrix-nap-info-jalin-kerja-sama-strategis-dengan-digital-realty-bersama-untuk-perkuat-ekosistem-infrastruktur-digital-nasional — Matrix NAP Info partnered with Digital Realty Bersama to strengthen Jakarta data center interconnection at its Matrix Data Center, citing rising data center, cloud, and AI computing demand as the driver.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>1a08a33c0e9b8bee</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:50+00:00</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-09-10T07:24:05+00:00</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2623,54 +2656,55 @@
           <t>https://xl.co.id</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/princeton-digital-group-to-acquire-majority-stake-in-xl-axiatas-indonesian-data-centers/ — Princeton Digital Group agreed to acquire a 70% stake in XL Axiata data center portfolio (5 sites: Pekanbaru, Cibitung, Surabaya, Bintaro, Bandung), with PDG committing US$100M growth capital to expand capacity of the existing facilities XL Axiata co-owns</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>bounced</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
         <is>
           <t>550 5.1.0 address not found (mailer-daemon)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:08+00:00</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2698,58 +2732,59 @@
           <t>https://morarepublic.co.id</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>web_research: https://www.morarepublic.co.id/our-company/news/moratelindo-dan-my-republic-indonesia-umumkan-merger-untuk-percepatan-dan-pemerataan-ekosistem-digital-di-indonesia — Merged with MyRepublic Indonesia in April 2026 to form PT Ekamas Mora Republik Tbk, combining six existing data centers (3.3MW total capacity) and national fiber networks to scale digital infrastructure and avoid capex duplication, per CEO Jimmy Kadir</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>1a08f5c18cb38e73</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:08+00:00</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:16+00:00</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2777,58 +2812,59 @@
           <t>https://www.bankmandiri.co.id</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>web_research: https://investortrust.id/financial/55633/perkuat-digitalisasi-bank-mandiri-siapkan-capex-it-rp-3-triliun-di-2025 — IT Director Timothy Utama announced Rp3 trillion 2025 IT capex directed at strengthened IT infrastructure and networks, alongside the new Mandiri Digital Tower housing the bank's IT/data center operations.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>1a091f9ccd394c53</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:45+00:00</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2856,58 +2892,59 @@
           <t>https://ioh.co.id</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>web_research: https://www.nokia.com/newsroom/indosat-ooredoo-group-nokia-and-nvidia-launch-zankore-by-indosat-ready-to-serve-the-region-with-full-stack-ai-infra-platform/ — CEO Vikram Sinha launched Zankore by Indosat, targeting 1 gigawatt of NVIDIA DGX AI Factory capacity (~200MW online 1H2027 on NVIDIA GB300 NVL72 systems) across centralized GPU infrastructure and AI data centers.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>1a091fac15d07b04</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:48+00:00</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2935,58 +2972,59 @@
           <t>https://www.telkom.co.id</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>web_research: https://www.telkom.co.id/sites/berita/id_ID/news/telkomgroup-siap-operasikan-hyperscale-data-center-neutradc-nxera-batam-dukung-ekosistem-ai-3387 — TelkomGroup preparing to operate the NeutraDC Nxera Batam hyperscale data center to support Indonesia's AI ecosystem, part of network/IT infrastructure expansion overseen by the Director of Network &amp; IT Solutions.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>1a091fa278587d7c</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:08+00:00</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3014,58 +3052,59 @@
           <t>https://www.komdigi.go.id</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>web_research: https://katadata.co.id/digital/teknologi/6815c63429082/pusat-data-nasional-beroperasi-juni-berikut-kecanggihan-dan-fungsinya — Operates Pusat Data Nasional (PDN) Cikarang, a Tier-4 national data center with 20MW electrical capacity expandable to 80MW, using a water-cooling system, described by the ministry as Indonesia's flagship integrated government data center.</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>1a091f995bf79daa</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:30+00:00</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3093,58 +3132,59 @@
           <t>https://ugm.ac.id</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>web_research: https://www.overclockingid.com/kemkomdigi-indosat-nvidia-dan-ugm-resmikan-pusat-ai-berbasis-universitas-pertama-di-indonesia/ — UGM, Komdigi, Indosat, and NVIDIA launched the UGM Indosat NVIDIA AI Technology Center, Indonesia's first university-based AI center, at GIK UGM in August 2026, with Rektor Ova Emilia citing UGM's ongoing AI infrastructure commitment since 2023.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>1a091fae13093edc</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:56+00:00</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3172,58 +3212,59 @@
           <t>https://www.telkom.co.id</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>web_research: https://www.telkom.co.id/sites/berita/id_ID/news/data-center-terisi-penuh-sebelum-beroperasi-telkom-percepat-ekspansi-kapasitas-neutradc-di-batam-3797 — Telkom's NeutraDC Nxera Batam hyperscale data center sold out before going operational, prompting Telkom to accelerate capacity expansion to support Indonesia's AI ecosystem.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>1a091fa094171db8</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:00+00:00</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3251,58 +3292,59 @@
           <t>https://www.bca.co.id</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>web_research: https://www.liputan6.com/saham/read/5467651/data-center-bca-bakal-beroperasi-pada-2025 — BCA's new Cikarang data center began full operations in 2025 as part of a High Availability System strategy combining cloud adoption, new data center construction, and AI-based data infrastructure modernization.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>1a091fa4534ae567</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:33+00:00</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3330,58 +3372,59 @@
           <t>https://www.bankmandiri.co.id</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>web_research: https://investor.id/finance/373950/resmikan-mandiri-digital-tower-menteri-bumn-perkuat-data-center-untuk-digitalisasi-bumn — Bank Mandiri inaugurated the 32-floor, ~70,000 sqm Mandiri Digital Tower as its new IT/data-center hub, with the Minister of SOEs calling for the bank to further strengthen its data center capacity.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>1a091f9ebe0603b0</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:53+00:00</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3409,58 +3452,59 @@
           <t>https://www.bni.co.id</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>web_research: https://www.cloudcomputing.id/berita/bni-transformasi-digital-ai-cloud — Director of Technology and Operations Toto Prasetio said AI and cloud adoption are key elements of BNI's digital transformation, discussed at the BNI Investor Daily Summit 2024.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>1a091fafde7aa858</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-09-11T19:39:03+00:00</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3488,58 +3532,59 @@
           <t>https://bri.co.id</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>web_research: https://www.hutamakarya.com/en/hutama-karya-lakukan-topping-off-proyek-it-center-bri-ragunan-paket-2-siap-dukung-transformasi-digital — BRI completed topping-off of the Cloud IT Center BRI Ragunan Package 2 building (Rp517B Package 1 contract with PTPP, Package 2 with Hutama Karya), a strategic national banking IT/data center; VP Rio Hendarwan said it will accelerate service digitalization.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>1a091fb1a559b904</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-09-11T19:39:11+00:00</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3567,58 +3612,59 @@
           <t>https://www.gotocompany.com</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>web_research: https://www.gotocompany.com/en/news/press/goto-group-tencent-cloud-and-alibaba-cloud-sign-agreement-to-boost-cloud-infrastructure-and-nurture-local-digital-talent-in-indonesia — CEO Patrick Walujo signed 5-year cloud infrastructure agreements with Tencent Cloud and Alibaba Cloud (incl. Tencent's 3rd Indonesia data center) to strengthen GoTo's onshore data/cloud infrastructure.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>1a091f9b1d90992f</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:38+00:00</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3646,58 +3692,59 @@
           <t>https://www.brin.go.id</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>web_research: https://www.brin.go.id/news/121592/brin-tekankan-pentingnya-high-performance-computing-mahameru-dukung-data-riset-indonesia — BRIN operates the Mahameru HPC supercomputing cluster (92 high-density nodes, NVIDIA DGX A100 GPU facility) across its Cibinong and Serpong science-park data centers, emphasized by leadership as critical national research computing infrastructure.</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>1a091faa52be4315</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:40+00:00</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3725,58 +3772,59 @@
           <t>https://www.ipb.ac.id</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>web_research: https://www.ipb.ac.id/news/index/2023/09/ipb-university-has-nvidia-dgx-a100-supercomputer-with-highest-performance-technology-in-indonesia/ — ARLab acquired an NVIDIA DGX A100 supercomputer, described by ARLab head Dr. Irdika Mansur as the highest-performance AI computing technology in Indonesia at the time, used for AI model development in agriculture/bioinformatics research</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>1a09479806a23b0c</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-09-12T07:16:32+00:00</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3804,58 +3852,59 @@
           <t>https://www.its.ac.id</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>web_research: https://www.its.ac.id/komputer/id/launching-nvidia-dgx-a100-artificial-intelligence-supercomputer-2/ai-supercomputer-2/ — Computer Engineering Dept launched an NVIDIA DGX-A100 AI supercomputer (Feb 2025), used by ITS's Center of AI and Digital Technology (AIDT) for high-performance computing research</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>1a09478fb98912ea</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:57+00:00</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3883,58 +3932,59 @@
           <t>https://www.ub.ac.id</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>web_research: https://www.itworks.id/71583/universitas-brawijaya-resmikan-ai-center.html — Inaugurated UB's AI Center (Feb 2023), which runs an NVIDIA DGX A100 supercomputer (5 petaFLOPS) for cross-disciplinary AI research, later formally opened nationally by the Minister of Communication and Digital Affairs (Jan 2025)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>1a094781562dc995</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:57+00:00</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3962,58 +4012,59 @@
           <t>https://www.del.ac.id</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>web_research: https://www.del.ac.id/?p=16932 — Launched AI Center (Aug 2026) with an NVIDIA DGX H200 supercomputer (up to 156.5 petaFLOPS national AI education capacity), making IT Del Indonesia's highest AI-computing-capacity education institution, per Wakil Rektor I Dr. Johannes Sianipar</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>1a09477ddd96a9aa</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:43+00:00</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4041,58 +4092,59 @@
           <t>https://telkomuniversity.ac.id</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>web_research: https://neucentrix.hk/telkom-is-the-first-user-of-the-most-advanced-ai-supercomputer-nvidia-dgx-a100-in-indonesia/ — Operates an NVIDIA DGX A100 AI supercomputer and an Artificial Intelligence Center (AIC) as a member of the government-formed Indonesia AI Research Consortium (IARC); its former AI research center chair Prof. Suyanto is now Rector</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>1a09478c7e27301d</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:44+00:00</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4120,58 +4172,59 @@
           <t>https://www.gunadarma.ac.id</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>web_research: https://www.hpc-hub.gunadarma.ac.id/ — Operates NVIDIA DGX-1 and DGX A100 supercomputers via its dedicated HPC/DGX development hub for AI and data-intensive research</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>1a094792988c4c06</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-09-12T07:16:19+00:00</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4199,58 +4252,59 @@
           <t>https://www.ub.ac.id</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>web_research: https://tugujatim.id/launching-artificial-intelligence-center-universitas-brawijaya-kolaborasikan-penelitian-antar-bidang-keilmuan/ — Appointed Head of UB's AI Center (Feb 2023), which operates an NVIDIA DGX A100 supercomputer (5 petaFLOPS) for AI/data-science research</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>1a094784229ff481</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:31+00:00</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,70 +449,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>lawful_basis</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>send_attempts</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>message_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>last_error</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>date_added</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>date_contacted</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>meeting_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>meeting_time</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>proposed_slots_json</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>meeting_notes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>meeting_updated</t>
         </is>
@@ -537,58 +542,59 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>web_research: https://zankore.com/ — Indosat, Ooredoo Group, Nokia and Nvidia launched Zankore, targeting 1GW of Nvidia DSX AI Factory capacity in Indonesia, with an initial ~200MW live in Jakarta by H1 2027</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>gmail:1a073bddc5d568b3</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,58 +619,59 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>web_research: https://dci-indonesia.com/news/dci-indonesia-inaugurates-e2-surabaya-expanding-its-platform-to-eastern-indonesia — Inaugurated E2 Surabaya (9MW IT load), its first data center in Eastern Indonesia, and separately raised a $980M loan to fund AI-era capacity expansion</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>gmail:1a073bd4a311c874</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -693,58 +700,59 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>web_research: https://www.digitaledgedc.com/resources/newsroom/digital-edge-4-5b-cgk-500mw-ai-ready-hyperscale-campus-indonesia/ — Announced a $4.5B investment in CGK Campus, a 500MW (scaling to 1GW) AI-ready hyperscale data center in Bekasi featuring direct-to-chip liquid cooling and a 1.25 target PUE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>gmail:1a073be6a2869476</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,58 +777,59 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>web_research: https://www.neutradc.com/news/60643/data-center-fully-secured-before-launch-telkom-indonesia-accelerates-expansion-of-neutradc-capacity-in-batam — Accelerating NeutraDC AI data center capacity in Batam (Nxera, 18MW initial phase scaling to 54MW) plus a 200MW Cikarang hyperscale expansion secured via a PLN power deal</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>gmail:1a073bd609a9863d</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -841,58 +850,59 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>web_research: https://www.bdxworld.com/locations/indonesia/ — Building BDx Jakarta CGK3, one of Indonesia's first liquid-cooled AI data center campuses, plus a $320M loan-backed expansion of CGK4/CGK5 to 1.2GVA for high-density AI workloads</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>gmail:1a073bdf45fcb5c0</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -913,58 +923,59 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>web_research: https://firmus.co/newsroom/firmus-to-build-170-000-gpu-ai-factor-y-campus-with-nvidia-for-global-ai-natives — Partnering with Nvidia on an 8-year deal to build a 360MW, 170,000-GPU AI Factory campus in Batam, Indonesia, going live Q1 2027</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>gmail:1a073be85a254b4e</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-09-05T20:38:49+00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-09-05T22:44:33+00:00</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -989,58 +1000,59 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>web_research: https://www.brin.go.id/en/news/122525/indonesia-and-korea-launch-hpc-supercomputer-encourage-asean-digital-collaboration — BRIN launched a Top500-ranked HPC supercomputer facility (MAHAMERU) with South Korea under the ASEAN-Korea Digital Innovation Flagship, accelerating scientific data processing from 10 hours to 10 seconds -- a compute density that requires serious thermal management</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>gmail:1a074b3d7bd7faf0</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1065,58 +1077,59 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>web_research: https://www.gawcapital.com/news/pressrelease/gaw-capital-partners-announces-the-launch-of-golden-digital-gateway-data-center-in-nongsa-digital-park-indonesia/ — Launched Golden Digital Gateway, a carrier-neutral colocation data center JV with Sinar Primera in Nongsa Digital Park, Batam -- 5.2MW first phase live, with a second phase planned to expand to 20MW</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>gmail:1a074b5557022ca6</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1141,58 +1154,59 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>web_research: https://blog.ionnetwork.co.id/ion-network-resmikan-prodc-data-center-bali-perkuat-infrastruktur-digital-indonesia-timur/ — Officially launched ProDC Data Center Bali and a new Denpasar regional office on 25 June 2026 to strengthen digital infrastructure in Eastern Indonesia, with plans to build a further data center in Semarang</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>gmail:1a074b44f85d0c6a</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1217,58 +1231,59 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>web_research: https://www.inilah.com/biznet-bangun-ai-data-center-pertama-di-bali-target-rampung-oktober-2025 — Building Indonesia's first AI-Ready Data Center in Jimbaran, Bali (Karang Mas Estate), targeted for completion October 2025, positioned as a high-capacity AI processing hub and AI technology development lab</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>gmail:1a074b3ecc4ed0a2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1293,58 +1308,59 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>web_research: https://www.antaranews.com/berita/5435506/omadata-hadir-di-makassar-guna-perkuat-infrastruktur-digital — Officially expanding into Makassar with a new E3 Data Center at CitraLand City CPI to serve as an eastern-Indonesia edge hub for the ~100 ISPs in the Sulampua region needing low-latency, high-reliability capacity</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>gmail:1a074b497e7836c4</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1369,58 +1385,59 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>web_research: https://www.rackscentral.com/news/racks-central-expands-footprint-with-new-land-acquisition-in-nongsa-digital-park-batam — Building a 95MW greenfield campus in Nongsa Digital Park, Batam, purpose-built for high-density compute and AI workloads with liquid-ready cooling and high rack power densities, backed by a $1B China-ASEAN investment fund commitment</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>gmail:1a074b4eb92f9e82</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2026-09-06T03:14:05+00:00</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1445,58 +1462,59 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>web_research: https://www.amazon.jobs/en/jobs/3187721/dceo-facility-manager-indonesia-data-center-engineering-operations — Actively hiring a DCEO Facility Manager for its Indonesia data center cluster to manage electrical/mechanical critical infrastructure (chillers, cooling towers, CRAH units, generators, UPS) supporting the AWS Asia Pacific (Jakarta) Region</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>1a0812521f679104</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:32+00:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1521,58 +1539,59 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>web_research: https://ugm.ac.id/en/news/ugm-partners-with-nvidia-and-indosat-to-advance-ai-research/ — Hosting the UGM Indosat NVIDIA AI Technology Center (opened August 2026), Indonesia's first university AI center, with an NVIDIA DGX Station AI supercomputer placed at the Faculty of Engineering and Faculty of Mathematics and Natural Sciences</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>1a08124e1a4af6af</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:15+00:00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1601,58 +1620,59 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>web_research: https://www.prnewswire.com/news-releases/nokia-blaize-and-datacomm-diangraha-unite-to-deliver-hybrid-ai-inference-across-indonesia-and-southeast-asia-302755505.html — Announced (April 2026) a strategic alliance with Nokia and Blaize to deploy hybrid AI inference infrastructure across Indonesia, with Datacomm's own leadership stating data centers must evolve toward GPU infrastructure to meet enterprise/public-sector AI demand</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>1a0812444a22266b</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:36+00:00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1677,58 +1697,59 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>web_research: https://www.nexdatacenter.com/locations/ — Operates multiple Tier III colocation facilities in Jakarta CBD (Cyber 2 Tower, Menara Tendean) purpose-built for high-density deployments up to 10kVA per rack, part of Indonesia's growing carrier-neutral colocation cluster</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>1a081250146ef7f5</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:24+00:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1753,58 +1774,59 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>web_research: https://spacedc.com/spacedcs-data-center-campus-first-in-indonesia-to-feature-advanced-cooling-technology-to-facilitate-energy-and-space-efficiencies/ — JAK1 Jakarta campus is first in Indonesia to feature advanced cooling technology (Vertiv thermal walls, N+1 high-efficiency air-cooled chillers with cogeneration absorption chillers, hot-aisle containment) with water-cooled racks up to 50kW each</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>1a08124bed10cf44</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:07+00:00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1833,58 +1855,59 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>web_research: https://newsroom.equinix.com/2025-05-15-Equinix-Unveils-Its-First-AI-Ready-Data-Center-with-Dense-Ecosystem-in-Jakarta — Inaugurated JK1, its first AI-ready IBX data center in Jakarta (JV with PT Astra International), with phase two adding liquid cooling and Cooling Array technology to support higher-density AI workloads at a target PUE of 1.41</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>1a0812481201f6c1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:51+00:00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1909,58 +1932,59 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/area31-to-invest-675m-in-depok-indonesia-data-center/ — Committing ~$67.5M over five years to expand its Depok (Cimanggis) hyperscale campus, including a new Data Hall 2 (150+ racks, 600kW capacity) at its AI-ready, carrier-neutral RATED 3 facility</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>1a08124a14825778</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:59+00:00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1985,58 +2009,59 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>web_research: https://www.biznetgio.com/en/product/neo-gpu — Launched NEO GPU cloud service offering up to 8x NVIDIA H200 GPUs per instance (3,958 TFLOPS, 1,128GB HBM3e with NVLink) for AI training/inference workloads hosted in its Indonesia data centers</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>1a08124631a7bea9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:43+00:00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2061,58 +2086,59 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>web_research: https://www.wowrack.com/en-us/blog/colocation/gpu-as-a-service/ — Offers GPU-as-a-Service (GPUaaS) out of its Jakarta and Surabaya data centers, giving AI teams on-demand access to GPU capacity without their own hardware investment, amid rising Indonesian AI/GPU infrastructure demand</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>1a0812564d07ef3e</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:50+00:00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2137,58 +2163,59 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>web_research: https://www.zettagrid.id/gpu-vworkstations/ — Offers Enterprise AI Instances powered by Dell servers with NVIDIA A100 and H100 GPUs, plus GPU vWorkstations, run on VMware infrastructure with NVIDIA AI Enterprise in its Indonesia data center</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>1a0812541647810f</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-09-08T13:10:26+00:00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>2026-09-08T13:11:40+00:00</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2209,58 +2236,59 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>web_research: https://www.lintasarta.net/en/news/lintasarta-presents-gpu-merdeka-an-advanced-sovereign-ai-cloud-for-indonesia-powered-by-nvidia-ai/ — Peruri's Digital Business Director Farah Fitria Rahmayanti participated in the launch of GPU Merdeka, Indonesia's NVIDIA-powered sovereign AI GPU-as-a-Service cloud, indicating Peruri is adopting GPU-accelerated AI infrastructure for its state digital security services</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>1a0850fb72832e3a</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:38+00:00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2281,58 +2309,59 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/telin-and-bw-digital-partner-on-batam-singapore-subsea-cable/ — Telin is building the new Nongsa-Changi Cable and INSICA subsea cable systems (landed Jul 2026 / ready Q4 2026) specifically to carry the surge in data-center-to-data-center traffic between Batam and Singapore, signaling major new DC interconnection capacity build-out</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>1a0850fd78650da2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:45+00:00</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2353,58 +2382,59 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>web_research: https://blogs.nvidia.com/blog/indonesia-ai-center-of-excellence — Building Indonesia's AI Center of Excellence with NVIDIA (Blackwell GPUs, NVIDIA Cloud Partner reference architectures) and Cisco (announced July 2025); also invested ~$200M in a Surakarta AI data center with NVIDIA and formed the Raia Grid JV to assemble NVIDIA GPUs domestically in Indonesia starting Dec 2026</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>1a0850f96f15772b</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:30+00:00</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2425,58 +2455,59 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/gds-partners-with-indonesias-sovereign-wealth-fund-for-batam-data-center-campus/ — GDS Holdings and Indonesia's sovereign wealth fund (INA) formed a JV building a 28MW hyperscale data center campus at Nongsa Digital Park, Batam, integrating GDS's Smart DC solution</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>1a0850ff74446503</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:21+00:00</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>2026-09-09T07:26:54+00:00</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2501,58 +2532,59 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>web_research: https://ekonomi.bisnis.com/read/20260206/47/1950875/intiland-dild-luncurkan-data-center-land-di-surabaya-berkapasitas-3mw — Intiland (via JV PT Inti Arunika Persada with ION Network) launched DC Land data center at Intiland Tower Surabaya Feb 2026, live at 3MW with ~50% capacity already occupied, targeting expansion to 30MW to serve East Indonesia demand.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>1a08a33a21b90f3b</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:50+00:00</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:58+00:00</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2577,58 +2609,59 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>web_research: https://napinfo.co.id/highlights/article/id/matrix-nap-info-jalin-kerja-sama-strategis-dengan-digital-realty-bersama-untuk-perkuat-ekosistem-infrastruktur-digital-nasional — Matrix NAP Info partnered with Digital Realty Bersama to strengthen Jakarta data center interconnection at its Matrix Data Center, citing rising data center, cloud, and AI computing demand as the driver.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>1a08a33c0e9b8bee</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-09-10T07:23:50+00:00</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>2026-09-10T07:24:05+00:00</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2657,54 +2690,55 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>web_research: https://www.datacenterdynamics.com/en/news/princeton-digital-group-to-acquire-majority-stake-in-xl-axiatas-indonesian-data-centers/ — Princeton Digital Group agreed to acquire a 70% stake in XL Axiata data center portfolio (5 sites: Pekanbaru, Cibitung, Surabaya, Bintaro, Bandung), with PDG committing US$100M growth capital to expand capacity of the existing facilities XL Axiata co-owns</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>bounced</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>550 5.1.0 address not found (mailer-daemon)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:08+00:00</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2733,58 +2767,59 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>web_research: https://www.morarepublic.co.id/our-company/news/moratelindo-dan-my-republic-indonesia-umumkan-merger-untuk-percepatan-dan-pemerataan-ekosistem-digital-di-indonesia — Merged with MyRepublic Indonesia in April 2026 to form PT Ekamas Mora Republik Tbk, combining six existing data centers (3.3MW total capacity) and national fiber networks to scale digital infrastructure and avoid capex duplication, per CEO Jimmy Kadir</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>1a08f5c18cb38e73</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:08+00:00</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2026-09-11T07:26:16+00:00</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2813,58 +2848,59 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>web_research: https://investortrust.id/financial/55633/perkuat-digitalisasi-bank-mandiri-siapkan-capex-it-rp-3-triliun-di-2025 — IT Director Timothy Utama announced Rp3 trillion 2025 IT capex directed at strengthened IT infrastructure and networks, alongside the new Mandiri Digital Tower housing the bank's IT/data center operations.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>1a091f9ccd394c53</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:45+00:00</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2893,58 +2929,59 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>web_research: https://www.nokia.com/newsroom/indosat-ooredoo-group-nokia-and-nvidia-launch-zankore-by-indosat-ready-to-serve-the-region-with-full-stack-ai-infra-platform/ — CEO Vikram Sinha launched Zankore by Indosat, targeting 1 gigawatt of NVIDIA DGX AI Factory capacity (~200MW online 1H2027 on NVIDIA GB300 NVL72 systems) across centralized GPU infrastructure and AI data centers.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>1a091fac15d07b04</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:48+00:00</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2973,58 +3010,59 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>web_research: https://www.telkom.co.id/sites/berita/id_ID/news/telkomgroup-siap-operasikan-hyperscale-data-center-neutradc-nxera-batam-dukung-ekosistem-ai-3387 — TelkomGroup preparing to operate the NeutraDC Nxera Batam hyperscale data center to support Indonesia's AI ecosystem, part of network/IT infrastructure expansion overseen by the Director of Network &amp; IT Solutions.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>1a091fa278587d7c</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:08+00:00</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3053,58 +3091,59 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>web_research: https://katadata.co.id/digital/teknologi/6815c63429082/pusat-data-nasional-beroperasi-juni-berikut-kecanggihan-dan-fungsinya — Operates Pusat Data Nasional (PDN) Cikarang, a Tier-4 national data center with 20MW electrical capacity expandable to 80MW, using a water-cooling system, described by the ministry as Indonesia's flagship integrated government data center.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>1a091f995bf79daa</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:30+00:00</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3133,58 +3172,59 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>web_research: https://www.overclockingid.com/kemkomdigi-indosat-nvidia-dan-ugm-resmikan-pusat-ai-berbasis-universitas-pertama-di-indonesia/ — UGM, Komdigi, Indosat, and NVIDIA launched the UGM Indosat NVIDIA AI Technology Center, Indonesia's first university-based AI center, at GIK UGM in August 2026, with Rektor Ova Emilia citing UGM's ongoing AI infrastructure commitment since 2023.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>1a091fae13093edc</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:56+00:00</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3213,58 +3253,59 @@
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>web_research: https://www.telkom.co.id/sites/berita/id_ID/news/data-center-terisi-penuh-sebelum-beroperasi-telkom-percepat-ekspansi-kapasitas-neutradc-di-batam-3797 — Telkom's NeutraDC Nxera Batam hyperscale data center sold out before going operational, prompting Telkom to accelerate capacity expansion to support Indonesia's AI ecosystem.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>1a091fa094171db8</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:00+00:00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3293,58 +3334,59 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>web_research: https://www.liputan6.com/saham/read/5467651/data-center-bca-bakal-beroperasi-pada-2025 — BCA's new Cikarang data center began full operations in 2025 as part of a High Availability System strategy combining cloud adoption, new data center construction, and AI-based data infrastructure modernization.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>1a091fa4534ae567</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:33+00:00</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3373,58 +3415,59 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>web_research: https://investor.id/finance/373950/resmikan-mandiri-digital-tower-menteri-bumn-perkuat-data-center-untuk-digitalisasi-bumn — Bank Mandiri inaugurated the 32-floor, ~70,000 sqm Mandiri Digital Tower as its new IT/data-center hub, with the Minister of SOEs calling for the bank to further strengthen its data center capacity.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>1a091f9ebe0603b0</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:53+00:00</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3453,58 +3496,59 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>web_research: https://www.cloudcomputing.id/berita/bni-transformasi-digital-ai-cloud — Director of Technology and Operations Toto Prasetio said AI and cloud adoption are key elements of BNI's digital transformation, discussed at the BNI Investor Daily Summit 2024.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>1a091fafde7aa858</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>2026-09-11T19:39:03+00:00</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3533,58 +3577,59 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>web_research: https://www.hutamakarya.com/en/hutama-karya-lakukan-topping-off-proyek-it-center-bri-ragunan-paket-2-siap-dukung-transformasi-digital — BRI completed topping-off of the Cloud IT Center BRI Ragunan Package 2 building (Rp517B Package 1 contract with PTPP, Package 2 with Hutama Karya), a strategic national banking IT/data center; VP Rio Hendarwan said it will accelerate service digitalization.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>1a091fb1a559b904</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>2026-09-11T19:39:11+00:00</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3613,58 +3658,59 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>web_research: https://www.gotocompany.com/en/news/press/goto-group-tencent-cloud-and-alibaba-cloud-sign-agreement-to-boost-cloud-infrastructure-and-nurture-local-digital-talent-in-indonesia — CEO Patrick Walujo signed 5-year cloud infrastructure agreements with Tencent Cloud and Alibaba Cloud (incl. Tencent's 3rd Indonesia data center) to strengthen GoTo's onshore data/cloud infrastructure.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>1a091f9b1d90992f</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>2026-09-11T19:37:38+00:00</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3693,58 +3739,59 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>web_research: https://www.brin.go.id/news/121592/brin-tekankan-pentingnya-high-performance-computing-mahameru-dukung-data-riset-indonesia — BRIN operates the Mahameru HPC supercomputing cluster (92 high-density nodes, NVIDIA DGX A100 GPU facility) across its Cibinong and Serpong science-park data centers, emphasized by leadership as critical national research computing infrastructure.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>1a091faa52be4315</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-09-11T19:36:51+00:00</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>2026-09-11T19:38:40+00:00</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3773,58 +3820,59 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>web_research: https://www.ipb.ac.id/news/index/2023/09/ipb-university-has-nvidia-dgx-a100-supercomputer-with-highest-performance-technology-in-indonesia/ — ARLab acquired an NVIDIA DGX A100 supercomputer, described by ARLab head Dr. Irdika Mansur as the highest-performance AI computing technology in Indonesia at the time, used for AI model development in agriculture/bioinformatics research</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>1a09479806a23b0c</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>2026-09-12T07:16:32+00:00</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3853,58 +3901,59 @@
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>web_research: https://www.its.ac.id/komputer/id/launching-nvidia-dgx-a100-artificial-intelligence-supercomputer-2/ai-supercomputer-2/ — Computer Engineering Dept launched an NVIDIA DGX-A100 AI supercomputer (Feb 2025), used by ITS's Center of AI and Digital Technology (AIDT) for high-performance computing research</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>1a09478fb98912ea</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:57+00:00</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3933,58 +3982,59 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>web_research: https://www.itworks.id/71583/universitas-brawijaya-resmikan-ai-center.html — Inaugurated UB's AI Center (Feb 2023), which runs an NVIDIA DGX A100 supercomputer (5 petaFLOPS) for cross-disciplinary AI research, later formally opened nationally by the Minister of Communication and Digital Affairs (Jan 2025)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>1a094781562dc995</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:57+00:00</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4013,58 +4063,59 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>web_research: https://www.del.ac.id/?p=16932 — Launched AI Center (Aug 2026) with an NVIDIA DGX H200 supercomputer (up to 156.5 petaFLOPS national AI education capacity), making IT Del Indonesia's highest AI-computing-capacity education institution, per Wakil Rektor I Dr. Johannes Sianipar</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>1a09477ddd96a9aa</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:43+00:00</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4093,58 +4144,59 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>web_research: https://neucentrix.hk/telkom-is-the-first-user-of-the-most-advanced-ai-supercomputer-nvidia-dgx-a100-in-indonesia/ — Operates an NVIDIA DGX A100 AI supercomputer and an Artificial Intelligence Center (AIC) as a member of the government-formed Indonesia AI Research Consortium (IARC); its former AI research center chair Prof. Suyanto is now Rector</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>1a09478c7e27301d</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:44+00:00</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4173,58 +4225,59 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>web_research: https://www.hpc-hub.gunadarma.ac.id/ — Operates NVIDIA DGX-1 and DGX A100 supercomputers via its dedicated HPC/DGX development hub for AI and data-intensive research</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>1a094792988c4c06</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>2026-09-12T07:16:19+00:00</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4253,58 +4306,59 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>web_research: https://tugujatim.id/launching-artificial-intelligence-center-universitas-brawijaya-kolaborasikan-penelitian-antar-bidang-keilmuan/ — Appointed Head of UB's AI Center (Feb 2023), which operates an NVIDIA DGX A100 supercomputer (5 petaFLOPS) for AI/data-science research</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>legitimate_interest_b2b_public_contact</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="inlineStr">
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>1a094784229ff481</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-09-12T07:14:30+00:00</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>2026-09-12T07:15:31+00:00</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4360,6 +4360,2575 @@
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>admin@idcloudhost.com</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alfian Pamungkas Sakawiguna</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>IDCloudHost</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://idcloudhost.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>web_research: https://arenalte.com/life/teknologi/ekosistem-ai-saas-idcloudhost-dedicated-server-enterprise/ — Launched enterprise-class GPU-tier Dedicated Server line across its multi-location data center architecture (incl. its own Bogor facility) explicitly to support AI/ML and SaaS workloads</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1a09d4f1dbf4c524</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aicenter@itb.ac.id</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Institut Teknologi Bandung (ITB) Center for Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://aicenter.itb.ac.id</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>web_research: https://itb.ac.id/center-for-artificial-intelligence and https://www.itb.ac.id/news/read/3055/home/optimizing-performance-and-efficiency-through-high-performance-computing — ITB operates a dedicated Center for Artificial Intelligence plus faculty-level High Performance Computing clusters supporting machine learning, NLP, computer vision and robotics research -- ongoing HPC capacity for AI research workloads</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1a09d4f4cdada08c</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bizdev@nscc.sg</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>National Supercomputing Centre (NSCC) Singapore</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.nscc.sg</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>web_research: https://www.nscc.sg/portfolio/item/reimagining-the-future-with-high-performance-computing-hpc/ — Singapore's national high-performance computing facility, providing HPC resources for AI and research computing needs across NUS, NTU, A*STAR and industry</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1a09d4ff92955ea9</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>boyang.li@ntu.edu.sg</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Li Boyang (Albert)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Director, High Performance Computing Centre, NTU / Associate Professor, CCDS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NTU High Performance Computing Centre</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.ntu.edu.sg/hpcc</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>web_research: https://www.ntu.edu.sg/hpcc — Operates NTU's High Performance Computing Centre supporting compute- and data-intensive HPC/AI workloads for the university's research community; NTU also hosts the FutureGrid Accelerator HVDC-AI testbed with STT GDC supporting &gt;1,000kW density racks</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1a09d4ff2133b4bf</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cassie@starhub.com</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cassie Fong</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Assistant Vice President, Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>StarHub</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.starhub.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>web_research: https://www.starhub.com/business/products-and-services/hosting-my-business/data-centre/hyperscale-data-centre.html — Hyperscale Data Centre (AirTrunk SGP1 partnership at Loyang) designed to a PUE of 1.3 using highly efficient cooling systems, described as Singapore's largest carrier-neutral data centre</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1a09d4fd94d0a043</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>contactus@nxera-dc.com</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Nxera (Singtel)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.nxera-dc.com</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>web_research: https://www.singtel.com/about-us/media-centre/news-releases/nxera-opens-data-centre — Opened DC Tuas, a 58MW AI-ready facility described as Singapore's highest power-density data center, hosting the country's largest direct-to-chip liquid cooling deployment (cross-checked via DCD, iTnews Asia, Capacity coverage of the same launch)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1a09d4faa25350eb</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>corpcomms@m1.com.sg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>M1 Limited</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.m1.com.sg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>web_research: https://www.m1.com.sg/business/products/data-center — Operates the M1 Data Centre with cold aisle containment racks and integrated temperature/power/humidity monitoring, recently expanded to approximately 900 server racks</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1a09d4fde0396188</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>corporate.secretary@linknet.co.id</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Edward Sanusi</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Director &amp; Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Link Net</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.linknet.co.id</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>web_research: https://www.linknet.co.id/en/newsroom/article/link-net-dan-zte-bangun-data-center-baru-di-surabaya — Built a new TIA942-A Rate 2+ certified data center in Surabaya with ZTE (300 racks combined with the upgraded Jakarta facility), CTO Edward Sanusi quoted on ensuring the data centers meet industry quality/reliability standards via multiple active power and cooling distribution paths (N+1)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1a09d4f23b2dc806</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>corporate.secretary@mayapadahospital.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mayapada Hospital</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://mayapadahospital.com</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>web_research: https://issuu.com/charlton_media/docs/hca-h1-2023/s/28475480 — Mayapada Healthcare Group (7 hospitals, 1,200+ beds) is deploying AI-driven diagnostics with GE HealthCare and building hospital-wide patient data integration across its network -- growing clinical AI compute demand across its facilities</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>1a09d4f608cafeb3</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>corporate.secretary@siloamhospitals.com</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>David Utama</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>President Director</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Siloam Hospitals</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.siloamhospitals.com</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>web_research: https://healthtechasia.co/technology-should-support-clinical-judgement-not-replace-it-inside-siloams-hospital-of-the-future/ — Building a centralised enterprise AI foundation model trained on its own clinical data held locally in Indonesia (not on external cloud infrastructure) for data-sovereignty reasons, targeted complete by Nov 2026 across its 41-hospital network -- implying on-prem/local GPU compute buildout</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1a09d4f29abe608e</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>corsec@elitery.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Astrid Erawan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Corporate Secretary</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Elitery</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://elitery.com</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>web_research: https://ir.elitery.com/perusahaan/ and https://baxtel.com/data-center/elitery-bogor — Operates Southeast Asia's first Uptime Institute Tier III certified data center in Bogor and is scaling AI platforms (Elipedia, Elitementor) while expanding regionally to Malaysia/Europe, increasing compute density needs at its own facility</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1a09d4f186498993</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>customer.care@pegadaian.co.id</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pegadaian</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://pegadaian.co.id</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>web_research: https://www.nutanix.com/company/customers/pt-pegadaian — Pegadaian deployed the Nutanix Cloud Platform across 100+ consumer-facing applications and partnered with Telkom Indonesia for Data Center Colocation and DRC infrastructure, while building a private cloud for database-as-a-service to support its AI/ITOps initiatives</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1a09d4f66adef359</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>datacenters@ironmountain.com</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Data Centers Sales</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Iron Mountain Data Centers Singapore (SIN-1)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.ironmountain.com/en-sg/data-centers/locations/apac/singapore-data-center</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/analysis/making-iron-mountain-singapore-asia/ — DCD's profile of Iron Mountain's Singapore SIN-1 facility (Serangoon, 7.3MW, Tier III, ISO27001, acquired from Credit Suisse) describes column-free data halls supporting tall racks up to 52U -- a real, operating high-density colocation facility.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1a09d5021c19f862</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>frances.teh@keppel.com</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Frances Teh</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Director, Corporate Communications, Keppel Ltd</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Keppel Data Centres</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.keppel.com</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/keppel-and-shell-to-launch-immersion-cooling-pilot-at-singapore-data-center/ — Piloting immersion cooling with Shell at a Singapore data center to explore high-efficiency cooling for future AI/HPC workloads; also building Keppel DC SGP9, a 25MW floating data centre using seawater cooling (cross-checked via jpt.spe.org and Keppel's own newsroom coverage of the SGP campus)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1a09d4f9f6feb20f</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>info@bukalapak.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Bukalapak</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.bukalapak.com</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>web_research: https://www.itb.ac.id/news/read/56978/home/itb-bukalapak-join-hands-to-establish-laboratory-for-artificial-intelligence-and-cloud — Bukalapak established and operates an Artificial Intelligence &amp; Cloud Computing Innovation Center at ITB providing dedicated servers/compute infrastructure for AI and cloud research, per then-CEO Achmad Zaky</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1a09d4f6d0f481ca</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>info@cmi.chinamobile.com</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sales &amp; Technical Enquiries</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>China Mobile International (Singapore)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.cmi.chinamobile.com</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/china-mobile-international-launches-singapore-dc/ — DCD reports CMI's Tai Seng facility is a 17,490 sqm, six-floor, 2,100+ rack Singapore data centre built to Uptime Tier III TCDD/TCCF standards and awarded IMDA-BCA Green Mark Platinum -- a purpose-built high-density colocation facility with formal green/efficiency certification.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1a09d501529a79a9</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>info@omnidc.co.id</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Omni Data Center Indonesia</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://omnidc.co.id</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>web_research: https://omnidc.co.id/ and https://www.datacentermap.com/indonesia/batam/omni-dc/ — Operates Tier 3, carrier-neutral, N+1 redundant colocation data centers in Batam (BTM1) and Jakarta serving Singapore-spillover demand; no named executive found, general company inbox used</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1a09d4f31cc7a67a</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>info@tech.gov.sg</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Media/General Enquiries</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GovTech Singapore</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.tech.gov.sg</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>web_research: https://www.tech.gov.sg/about-us/what-we-do/our-digital-government-efforts/ai-and-data-driven-government/ — Runs Government on Commercial Cloud (GCC), with over 70% of eligible government systems now on commercial cloud infrastructure, unlocking AI capabilities (Gemini 2.5 Flash, Vertex AI Search) across public-sector agencies</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1a09d4fecf627095</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>investor.relations@cimbniaga.co.id</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Billie Setiawan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Head of Data Analytics and AI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CIMB Niaga</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.cimbniaga.co.id</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>web_research: https://www.googlecloudpresscorner.com/2026-04-14-CIMB-Niaga,-Google-Cloud,-and-Artefact-Debut-Enterprise-AI-Agents-to-Deliver-Life-Centric-Banking-for-Millions-of-Indonesians — Billie Setiawan, Head of Data Analytics and AI, quoted on CIMB Niaga's April 2026 launch (with Google Cloud and Artefact) of enterprise AI agents built by its in-house AI Center of Excellence on Google Cloud's full-stack AI infrastructure</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1a09d4f3c61cade3</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>investor.relations@mitratel.co.id</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Theodorus Ardi Hartoko</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Direktur Utama (President Director)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Mitratel</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.mitratel.co.id</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>web_research: https://kumparan.com/kumparanbisnis/mitratel-mau-bikin-mini-data-center-sebagai-ekosistem-digital-1yaHOjcri8E — President Director Theodorus Ardi Hartoko quoted on Mitratel's transformation into an integrated digital infrastructure provider building Mini Data Centers near mobile users as part of its 'Beyond Tower' edge infrastructure strategy</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1a09d4f36fcce6f8</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>itcare@nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NUS IT Care</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NUS IT (High Performance Computing)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://nusit.nus.edu.sg/hpc/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>web_research: https://nusit.nus.edu.sg/hpc/ — NUS IT provides centralized HPC infrastructure services to support NUS faculty, researchers and students across campus for compute-intensive research workloads</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1a09d4fff566fa27</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>jong@digitalrealty.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Joyce Ng</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Senior Communications Lead, Asia Pacific</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Digital Realty</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.digitalrealty.com</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>web_research: https://investor.digitalrealty.com/news-releases/news-release-details/digital-realty-selected-develop-50-megawatts-new-data-center — Selected by Singapore's EDB/IMDA to develop 50MW of new data center capacity, part of a nearly S$7 billion investment to strengthen Singapore as an APAC AI hub</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1a09d4f994acd464</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>laurenmy@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lauren Myers Cavanagh</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Senior Director of Communications, Asia</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Singapore</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/microsoft-commits-to-55bn-ai-and-cloud-investment-in-singapore-by-2029/ — Committed $5.5B to AI and cloud infrastructure investment in Singapore through 2029; stood up approximately 1GW of data center capacity in the prior three months as of a January 2026 announcement</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1a09d4fb77404f62</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>media@airtrunk.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AirTrunk</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://airtrunk.com</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapore-selects-equinix-microsoft-airtrunk-and-gds-for-80mw-data-center-trial/ — AirTrunk-ByteDance consortium awarded new data center capacity by Singapore's EDB/IMDA under the DC-CFA pilot; AirTrunk separately developing SGP2, one of Singapore's largest upcoming data centers at 70MW+</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1a09d4fb2595ebd7</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>media@dayonedc.com</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Media Contact</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DayOne Data Centers</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://dayonedc.com</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>web_research: https://www.dbs.com/newsroom/DayOne_secures_SGD_530_million_green_loan_from_DBS_OCBC_and_UOB_for_its_first_Singapore_data_centre — Building its first Singapore data centre (20MW), incorporating hybrid air and liquid cooling technologies and on-site Solid Oxide Fuel Cell power generation; achieved BCA Green Mark Platinum (Provisional)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1a09d4fd2937dd3a</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>pandawa@bpjs-kesehatan.go.id</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BPJS Kesehatan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.bpjs-kesehatan.go.id</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>web_research: https://www.cloudcomputing.id/berita/bpjs-kesehatan-tingkatkan-layanan-ai-big-data — BPJS Kesehatan invested in GPUs to build AI agents that verify hundreds of thousands of health claim documents for its 280 million participants nationwide -- a national-scale GPU compute deployment</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1a09d4f542a64b6a</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>press@google.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Press/Media Relations</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Google Cloud Singapore</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/google-completes-expansion-of-singapore-data-center-and-cloud-region/ — Completed the latest phase of its Singapore data center and cloud region campus expansion, bringing total technical infrastructure investment in Singapore to US$5 billion</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1a09d4fbc58598f8</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>press@meta.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Press/Media Relations</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Meta Singapore</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://datacenters.atmeta.com</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>web_research: https://www.metacareers.com/blog/singapore-data-center/ — Meta's Singapore Data Center is its first custom-built hyperscale facility in Asia and only APAC data center -- an 11-story, ~150MW building requiring purpose-built cooling design for Singapore's tropical climate</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1a09d4fc3e651845</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>qsm@imda.gov.sg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jo-Anne Tan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Quality Service Manager</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Infocomm Media Development Authority (IMDA)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.imda.gov.sg</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>web_research: https://isomer-user-content.by.gov.sg/38/c49f426a-8053-4c7f-bbaa-8437b743a18f/files-Speeches%202024-1__Factsheet_IMDA_Green_DC_Roadmap.pdf — IMDA's Green Data Centre Roadmap requires new data center capacity (DC-CFA2, 200MW+ call) to hit a PUE of 1.25 at 100% IT load, driving industry-wide adoption of liquid cooling (direct-to-chip, rear-door heat exchange, immersion) -- note: IMDA is the regulator setting these requirements, not an operator itself, so this is a policy-influence/we</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1a09d4fe79f5b578</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sales@1-net.com.sg</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sales Enquiries</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1-Net Singapore</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.1-net.com.sg</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/1-net-launches-new-data-center-in-singapore/ — DCD reports 1-Net North, a S$130m+ (with a further S$70m fit-out) purpose-built facility, became the first commercial data centre in Southeast Asia certified Tier III Constructed Facility by the Uptime Institute -- a real, capital-intensive high-density colocation build.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1a09d501ab3e936f</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sales@bd-dc.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Angelo Syailendra</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Bersama Digital Data Centers (Digital Realty Bersama)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.bd-dc.com</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/digital-realty-expands-into-indonesia-forms-jv-with-bersama-digital-infrastructure-asia/ and https://www.mingtiandi.com/real-estate/data-centres/digital-realty-enters-indonesia-data-centre-market-with-bersama/ — Digital Realty formed a 50:50 JV with Bersama Digital Infrastructure Asia in March 2025; CEO Angelo Syailendra continues leading BDDC's Jakarta campuses (CGK10/CGK11) scaling to 32MW with scalable power densities and advanced cooli</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1a09d4f5a0396323</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>salessingapore@globalswitch.com</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sales &amp; Customer Service, Global Switch Singapore</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Global Switch Singapore</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.globalswitch.com/data-centres/singapore/</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>web_research: https://www.globalswitch.com/data-centres/singapore/ — Global Switch's own Singapore data centres page states the Tai Seng and Woodlands campuses 'support the full spectrum of density needs, from entry-level to AI-grade high-density with air or liquid cooling' -- a direct, self-described high-density/liquid-cooling capacity signal at two active Singapore facilities.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1a09d500fc7caa46</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>yi.chow@sttelemediagdc.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chow Yi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Media Contact, ST Telemedia Global Data Centres</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ST Telemedia Global Data Centres</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.sttelemediagdc.com</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>web_research: https://www.sttelemediagdc.com/sg-en/newsroom/stt-gdc-launches-southeast-asia-first-hvdc-powered-ai-infrastructure-testbed — Launched Southeast Asia's first HVDC-powered AI infrastructure testbed (FutureGrid Accelerator) at NTU, designed to support ultra-high-density AI racks exceeding 1,000kW</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1a09d4fa4d6b6d00</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -5487,28 +5487,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1a09d4f6d0f481ca</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>550 5.1.1 The email account that you tried to reach does not exist. (mailer-daemon, Bukalapak)</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>2026-09-14T00:25:16+00:00</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2026-09-14T00:27:10+00:00</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6925,6 +6925,1988 @@
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>andrea.ng@capitaland.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Andrea Ng</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Investor Enquiries Contact</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CapitaLand Ascendas REIT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.capitaland.com</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>web_research: https://www.capitaland.com/en/about-capitaland/newsroom/news-releases/international/2026/march/capitaland-ascendas-reit-acquires-two-assets-in-Singapore-and-enters-Japan-with-a-hyperscale-data-centre.html — CapitaLand Ascendas REIT expanded its Singapore high-density data-centre portfolio (Ascendas Tech Park Data Center targets hyperscale/enterprise high-density colocation demand) via a S$1.4B acquisition including its first hyperscale data centre entry in Japan</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1a0a2de35a9b5215</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>corpcomms@micron.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Manish Bhatia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Executive Vice President, Global Operations</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Micron Singapore</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.micron.com</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>web_research: https://www.globenewswire.com/news-release/2026/01/27/3226056/14450/en/micron-breaks-ground-on-advanced-wafer-fabrication-facility-in-singapore.html — Micron broke ground on a ~US$24B advanced wafer fabrication facility in Singapore (700,000 sq ft cleanroom) plus a separate ~US$7B HBM advanced packaging facility, both driven by AI/data-centric memory demand; EVP Global Operations Manish Bhatia quoted on the investment</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1a0a2de15f84971f</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>corporate.secretary@mncland.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Corporate Secretary</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PT MNC Land Tbk</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.mncland.com</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/mnc-to-build-data-center-in-lido-resort-city-south-of-jakarta-indonesia/ — Partnering with PT Infokom Elektrindo to build a Techno Park with data center and AI center inside KEK MNC Lido City, part of a site with 450MW+ of total planned capacity</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1a0a2dd9886fbd3b</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cs@rspondokindah.co.id</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>RS Pondok Indah Group</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.rspondokindah.co.id</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>web_research: https://www.healthcareitnews.com/news/asia/rs-pondok-indah-group-clinches-first-stage-7-emram-indonesia — First hospital group in Indonesia to achieve HIMSS EMRAM Stage 7, building fully digital EMR infrastructure with automated device connectivity across its 3 hospitals</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>1a0a2dd906b35ca1</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>feedback@dsta.gov.sg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>General Feedback</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DSTA (Defence Science and Technology Agency)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.dsta.gov.sg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>web_research: https://www.oracle.com/news/announcement/dsta-selects-oracle-cloud-infrastructure-for-ministry-of-defence-singapore-2025-03-19/ — DSTA selected Oracle Cloud Infrastructure to build an air-gapped Oracle Cloud Isolated Region supporting MINDEF and the Singapore Armed Forces, giving them sovereign cloud computing, data management and AI infrastructure; DSTA's own InfoComm Infrastructure programme also designs/manages cloud data centres for MINDEF/SAF and Whole-of-Government C3 systems</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1a0a2de5225ef463</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>gallant@gallantventure.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Gallant Venture Ltd (Bintan Data Center Hub)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.gallantventure.com</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>web_research: https://www.forbes.com/sites/ardianwibisono/2025/10/27/dci-indonesia-tycoon-anthoni-salims-gallant-venture-building-data-center-hub-near-singapore/ — Jointly building with DCI Indonesia a gigawatt-scale data center complex on a 700-hectare site on Bintan Island near Singapore, targeted ready by 2027</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>1a0a2dd8aa8fa00b</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>halo@ikn.go.id</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (IKN Authority)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.ikn.go.id</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>web_research: https://konstruksimedia.com/otorita-ikn-dan-ustda-perkuat-kolaborasi-ai-dan-data-untuk-wujudkan-nusantara-sebagai-kota-cerdas/ — Building AI/data-driven smart city infrastructure for Indonesia's new capital Nusantara, in collaboration with USTDA and tech partners (Honeywell, Cisco, IBM, Google) including a smart-city command center</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>1a0a2dda324ee80c</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>helpdesk@kemkes.go.id</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI (SATUSEHAT)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://satusehat.kemkes.go.id</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0811-1050-0567</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>web_research: https://satusehat.kemkes.go.id/data — Operates SATUSEHAT, a national health-data integration platform running on cloud infrastructure processing nationwide EMR/health facility data, with AI initiatives for 5 priority diseases</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>1a0a2dddfe0be885</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>htx_contact@htx.gov.sg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HTX (Home Team Science and Technology Agency)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.htx.gov.sg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>web_research: https://www.htx.gov.sg/who-we-are/what-we-do/the-htxai-movement — HTX built NGINE, the Ministry of Home Affairs' first enterprise-grade AI compute infrastructure, spanning 30+ integrated technologies across compute, orchestration, networking and observability to support LLM training/modelling/simulation at scale</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>1a0a2de584f514f6</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>humas@bmkg.go.id</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BMKG (Badan Meteorologi, Klimatologi, dan Geofisika)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>web_research: https://www.bmkg.go.id/berita/bmkg-luncurkan-superkomputer-smong-perkuat-sistem-peringatan-dini-multi-hazards — Launched SMONG supercomputer (5 PFlops combined CPU+GPU across HPC MMS and HPC SMONG clusters) for multi-hazard early warning and AI-based weather modeling, one of the fastest HPC systems in Southeast Asia</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>1a0a2ddaf337367c</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>humas@bpbatam.go.id</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BP Batam (Badan Pengusahaan Batam)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://bpbatam.go.id</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>web_research: https://ptsp.bpbatam.go.id/en/bp-batam-kawal-investasi-rp88-triliun-ai-data-centre-untuk-transformasi-digital-batam/ — Government authority fast-tracking and overseeing a USD 5 billion (Rp88 trillion) High-Density AI Data Centre investment in Nongsa, Batam</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>1a0a2dde425c1176</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>humas@unud.ac.id</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Universitas Udayana (UCEAI - Pusat Kajian Kecerdasan Artifisial)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://uceai.unud.ac.id</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>web_research: https://uceai.unud.ac.id/ — Runs a dedicated AI research center (UCEAI) focused on AI development, research and application for Bali and Eastern Indonesia</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>1a0a2dda98245850</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>info@big.go.id</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Badan Informasi Geospasial (BIG)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.big.go.id</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>web_research: https://www.antaranews.com/berita/409549/big-bangun-data-center-raksasa-geospasial — Built a large-scale geospatial data center (300TB, expanding toward 1000TB) with Fujitsu and is developing an Integrated Map Production Center using HPC infrastructure</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>1a0a2ddcda6c321e</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>info@biofarma.co.id</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PT Bio Farma (Persero)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.biofarma.co.id</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>web_research: https://www.biofarma.co.id/en/latest-news/detail/bio-farma-and-google-cloud-indonesia-agree-on-the-mou-for-cooperation-in-healthcare-digital-transformation — Signed MoU with Google Cloud Indonesia for IaaS/PaaS/SaaS infrastructure supporting AI/ML for bioinformatics R&amp;D (vaccine and compound modeling)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>1a0a2ddd2fdeb81e</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>info@kpu.go.id</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Komisi Pemilihan Umum (KPU) Republik Indonesia</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.kpu.go.id</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>web_research: https://www.kpu.go.id/berita/baca/12716/kpu-siapkan-data-center-pemantauan-sirekap-pilkada — Preparing a dedicated data center to monitor the Sirekap election-recapitulation system for Pilkada, processing nationwide vote data</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>1a0a2ddd8ffd8b99</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>info@pupuk-indonesia.com</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PT Pupuk Indonesia (Persero)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.pupuk-indonesia.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0811 1000 1959</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>web_research: https://cloud.google.com/customers/pupuk — Runs Data Center (DC) and Disaster Recovery Center (DRC) infrastructure and uses AI/Vision AI (Google Cloud) plus 32,000 factory sensors across its fertilizer manufacturing operations</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1a0a2ddc1b478c4f</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>janice.yeo@silicon-box.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Janice Yeo</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Press Contact</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Silicon Box</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.silicon-box.com</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>web_research: https://www.silicon-box.com/silicon-box-launches-2-billion-state-of-the-art-advanced-semiconductor-packaging-fab-in-singapore-to-accelerate-the-future-of-computing-and-the-ai-era — Launched a $2B advanced semiconductor packaging (chiplet interconnection) fab at Tampines Wafer Fab Park, Singapore -- a 73,000 sqm facility built specifically to accelerate AI-era computing, now shipping 250M+ units</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>1a0a2de1abdf8fb7</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>jtc_comms_div@jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Christine Wong</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Assistant Chief Executive (Cluster Group)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>JTC Corporation</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>web_research: https://www.jtc.gov.sg/jurongisland/story-articles/nus-and-jtc-join-forces-to-power-jurong-island-green-transition — JTC has set aside 20 hectares on Jurong Island for Singapore's largest low-carbon Data Centre Park (up to 700MW); JTC signed an MOU with NUS to study a Sustainable Tropical Data Centre Testbed Phase 2.0 piloting direct-to-chip and immersion liquid cooling plus seawater-based heat rejection for AI-class density, with Assistant CEO Christine Wong presenting the MOU</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1a0a2de0eca46360</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>kominfo@jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Diskominfo Provinsi Jawa Timur</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://kominfo.jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>web_research: https://kominfo.jatimprov.go.id/berita/diskominfo-jatim-peroleh-sertifikasi-iso-27001-2022-untuk-data-center — Operates a provincial data center (with Disaster Recovery Center) serving all Pemprov Jatim agencies plus 16 district/city governments, ISO 27001:2022 certified</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1a0a2dd9ca0ed4a8</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>lily.ho@sgx.com</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ho Lily</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Singapore Exchange (SGX)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.sgx.com</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>web_research: https://investorrelations.sgx.com/news-releases/news-release-details/sgx-offers-fastest-connection-its-markets — SGX's own 'Reach' initiative was a $250M project to build a world-class data centre with the world's fastest trading engine and lowest trading latency for its Singapore co-location infrastructure, which continues to host SGX's critical trading systems</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>1a0a2de4bdd5b10c</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>marilyn.tan@mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Marilyn Tan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mapletree Investments</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>web_research: https://www.mapletree.com.sg/newsroom/mapletree-investments-and-mapletree-industrial-trust-to-acquire-us1-4-billion-data-centre-portfolio-in-north-america-from-digital-realty/ — Mapletree develops and owns purpose-built high-tech data centres in Singapore (STT Tai Seng 1, Equinix SG3, Mapletree Sunview 1) and continues expanding its global data-centre portfolio, including a US$1.4B North American DC acquisition</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>1a0a2de457e92620</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>partnership@apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Angkasa Pura Sarana Digital (APSD)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>web_research: https://investor.id/business/314676/angkasa-pura-ii-jajaki-pembangunan-data-center-di-bandara-soekarno-hatta — Angkasa Pura II's digital subsidiary exploring construction of a data center at Soekarno-Hatta Airport as part of a 'Smart Connected Airport' strategy</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>1a0a2ddc6ec22fdb</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sales@leaseweb.com</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Leaseweb Singapore</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.leaseweb.com</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>web_research: https://www.leaseweb.com/en/press/releases/significant-momentum-in-singapore-with-continued-apac-expansion — Leaseweb operates multiple Singapore data centres (SIN-01, SIN-12) offering colocation (rack/full rack/cage), reporting significant momentum and continued APAC expansion out of Singapore</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1a0a2de5f104a385</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sales@telehouse.com</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sales Enquiries</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Telehouse Singapore</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.telehouse.com</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>web_research: https://www.telehouse.com/global-data-centers/asia/singapore-data-centers/telehouse-singapore/ — Telehouse's Tier 3+ Chai Chee, Singapore facility runs an N+2 redundancy climate-control cooling system with rack power extendable up to 5kVA, part of its carrier-neutral colocation offering in Singapore</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>1a0a2de2ffffd072</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sales@utacgroup.com</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sales Enquiries</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>UTAC Group</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://utacgroup.com</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>web_research: https://www.plasmatherm.com/repeat-order-with-utac/ — UTAC's Singapore advanced packaging and test facility purchased a repeat Singulator 300 plasma dicing system to expand die-singulation/advanced-packaging capacity, supporting growing WLCSP packaging demand at its Singapore site</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>1a0a2de28cb6b15f</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>vis_pr@vis.com.tw</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Media Relations (Vanguard International Semiconductor, majority JV partner)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VSMC (VisionPower Semiconductor Manufacturing Company)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.vis.com.tw</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>web_research: https://www.globenewswire.com/news-release/2024/12/04/2991195/0/en/VSMC-Celebrates-Breaking-Ground-on-300mm-Fab-in-Singapore.html — VSMC (JV between Vanguard International Semiconductor and NXP) broke ground on a ~US$6.7-7.8B 300mm wafer fab in Tampines, Singapore, targeting 44,000 wafers/month for automotive, industrial and power semiconductor demand</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>1a0a2de229c3f27c</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -7128,28 +7128,24 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>1a0a2dd9886fbd3b</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>550 5.1.1 No Such User Here (mailer-daemon, PT MNC Land Tbk)</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:20:52+00:00</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
           <t>none</t>
@@ -8490,28 +8486,24 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>1a0a2de457e92620</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>550 5.4.1 Recipient address rejected: Access denied (mailer-daemon, Mapletree Investments)</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:21:23+00:00</t>
-        </is>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr">
         <is>
           <t>none</t>
@@ -8563,28 +8555,24 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>1a0a2ddc6ec22fdb</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>550 5.1.2 DNS Error: domain apsdigital.co.id not found / NXDOMAIN (mailer-daemon, Angkasa Pura Sarana Digital)</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:20:52+00:00</t>
-        </is>
-      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8895,6 +8895,164 @@
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>bd@aseglobal.com.sg</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ASE Singapore Pte Ltd</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.aseglobal.com.sg</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>web_research: https://www.digitimes.com/news/a20250519PD208/ase-singapore-testing-investment-siph.html — ASE is expanding and reinventing its Singapore chip-testing operations, investing in silicon photonics and co-packaged optics (CPO) test capability, positioning its Singapore site within Southeast Asia's AI data-center supply chain</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>1a0a801752096178</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:47+00:00</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>media@esr.com</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Philemon Foo</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Group Communications Manager, ESR</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ESR Group</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.esr.com</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>web_research: https://www.esr.com/news/esr-appoints-dalmar-sheikh-ceo-data-centres/ — ESR appointed Dalmar Sheikh as CEO of ESR Data Centres (effective 1 Sept 2026), based in Singapore, to lead the group's data centre platform, which carries a pipeline of more than 3.2GW across major Asia-Pacific markets amid rising hyperscaler and enterprise AI demand</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>1a0a8016ebbaec1e</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:47+00:00</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -6731,28 +6731,24 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>1a09d4f5a0396323</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SMTP 4.4.1: The recipient server did not accept our requests to connect (bd-dc.com timed out on all MX hosts); Gmail gave up after retrying, final DSN Action: failed, Last-Attempt-Date Wed 16 Sep 2026 21:16:49 -0700</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>2026-09-14T00:25:16+00:00</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>2026-09-14T00:27:10+00:00</t>
-        </is>
-      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U111"/>
+  <dimension ref="A1:U112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9049,6 +9049,83 @@
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sales@gorilla-technology.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Gorilla Technology Group</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.gorilla-technology.com</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/gorilla-technology-secures-25bn-gpuaas-contract-in-indonesia/ — Signed a transformational US$2.5B, 5-year AI GPUaaS compute contract anchored at NeutraDC's Batam, Indonesia data center; first phase (~1,000 NVIDIA B300 GPU servers) targets deployment in September 2026, a high-density GPU buildout requiring serious thermal management</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>1a0c34a3062b0171</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:26:59+00:00</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U112"/>
+  <dimension ref="A1:U115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9126,6 +9126,241 @@
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>business@balifiber.id</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PT Bali Towerindo Sentra Tbk (Balitower / Balifiber Data Center)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.balifiber.id</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>web_research: https://www.balifiber.id/home/bt_datacenter ; cross-checked via https://tiaonline.org/942-datacenter/pt-bali-towerindo-sentra-tbk-bali-tower-sentra-data-center-jl-batu-ceper-no-53-kebon-kelapa-gambir-jakarta-pusat-10120/ and https://www.idnfinancials.com/archive/45596/bali-towerindo-sentra-reinforce-data-centre-cctv-business — IDX-listed tower/infrastructure operator (BALI) runs Balitower/Balifiber Data Center in Jakarta Pusat, a TIA-942 Rated 3 certified facility that has expanded</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>1a0c6dfee1d86767</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ir@gds-services.com</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Laura Chen</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Investor Relations, GDS Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>GDS International (GDS Holdings)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.gds-services.com</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/gds-acquires-singapore-warehouse-plans-data-center-redevelopment/ — GDS International (CEO Jamie Khoo) acquired a S$112.8M / 39,978 sqm site at 21 Jalan Buroh, Jurong East, Singapore for a new hyperscale data center, part of an 80MW EDB/IMDA capacity award shared with Equinix, Microsoft and AirTrunk</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>1a0c6dfe66d4f732</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>junhong@nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Wang Junhong</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Senior Manager (HPC-AI), NUS Information Technology</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NUS IT (High Performance Computing)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://nusit.nus.edu.sg/hpc/</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>web_research: https://nusit.nus.edu.sg/hpc/wang-jun-hong (cross-checked via independent WebSearch query returning the same address, per this session's WebFetch-egress-blocked fallback protocol) — Named Senior Manager for NUS's centralized HPC-AI computing infrastructure (multi-core clusters, GPU accelerators) supporting compute-intensive research workloads across NUS -- a facilities/technical-operations-tier contact, not the general IT helpdesk inbox already on file</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>1a0c6dfdf93c8b16</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -9163,28 +9163,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>1a0c6dfee1d86767</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>550 5.1.1 &lt;business@balifiber.id&gt;: Recipient address rejected: balifiber.id (mailer-daemon, 2026-09-22)</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>2026-09-22T02:08:54+00:00</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>2026-09-22T02:09:24+00:00</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9357,6 +9357,387 @@
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ad_wibawa@its.ac.id</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Ir. Adhi Dharma Wibawa, S.T., M.T.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Head (Kepala Pusat), Center of AI and Digital Technology (AIDT/KATD)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>web_research: https://www.its.ac.id/katd/en/prof-dr-ir-adhi-dharma-wibawa-s-t-m-t/ ; cross-checked via a second independently-worded WebSearch query confirming ad_wibawa@its.ac.id appears on the AIDT/KATD centers own webinar content pages (per WebFetch-egress-blocked fallback protocol) -- Head of the ITS center that itself operates the NVIDIA DGX-A100 AI supercomputer cited in the existing ITS prospects.csv row (https://www.its.ac.id/komputer/id/launching-nvidia-dgx-a100-artificial-intelligence-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d60f76f22a</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>jacqueline_poh@jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jacqueline Poh</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>JTC Corporation</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>web_research: https://www.mingtiandi.com/real-estate/data-centres/singapore-plans-700mw-data-centre-park-on-jurong-island/ — JTC set aside 20 hectares on Jurong Island for Singapore's largest low-carbon Data Centre Park (up to 700MW); CEO Jacqueline Poh personally quoted on the project as JTC's bold step to build infrastructure for this new low-carbon data-centre hub</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d6c7aa1d75</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>mardhani@ugm.ac.id</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Dr. Mardhani Riasetiawan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Head of Digital Transformation Bureau (Kepala Biro Transformasi Digital)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Universitas Gadjah Mada</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>web_research: https://ugm.ac.id/en/news/ugm-partners-with-nvidia-and-indosat-to-advance-ai-research/ ; cross-checked via https://acadstaff.ugm.ac.id/mardhaniriasetiawan and https://mardhani.staff.ugm.ac.id/ (per WebFetch-egress-blocked fallback protocol, two independently-worded WebSearch queries both returned mardhani@ugm.ac.id) — Coordinated the UGM Indosat NVIDIA AI Technology Center launch (NVIDIA DGX Station AI supercomputer at Faculty of Engineering/Faculty of Mathematics and Natural Scien</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d59d1eafe3</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>media@bridgedatacentres.com</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Media Enquiries</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Bridge Data Centres</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">web_research: https://www.datacenterdynamics.com/en/news/bridge-data-centres-plans-to-invest-23bn-4bn-in-singapores-digital-infrastructure/ — CEO Eric Fan stated Bridge Data Centres plans to invest up to S$5B (~US$3.9B) in Singapore AI infrastructure, with research programs and facilities tied to advanced power architectures, next-generation cooling systems, AI-enabled operations, and energy optimization for high-density computing (cross-checked via Bloomberg and Mingtiandi coverage of the same </t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d66a738f75</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>phoebe.ewe@empyriondigital.com</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Phoebe Ewe</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VP, Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Empyrion Digital</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>web_research: https://empyriondigital.com/quantum-safe-and-ai-ready-empyrion-digitals-singapore-hub-expands-local-footprint-with-over-s1-1-billion-investment/ — Empyrion Digital (Singapore-HQ'd) investing over S$1.1B to expand Singapore data-centre capacity for high-density AI/cloud workloads; SG1 facility targets PUE below 1.20 and Green Mark Platinum certification; Phoebe Ewe is the named press contact on the company's own Singapore and Taiwan groundbreaking release boilerplate</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d739efeb23</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U120"/>
+  <dimension ref="A1:U124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9738,6 +9738,326 @@
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>fariz@ui.ac.id</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Fariz Darari, S.Kom., M.Sc., Ph.D.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Faculty in Charge, Tokopedia-UI AI Center of Excellence</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Universitas Indonesia - Fasilkom (Tokopedia-UI AI Center)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://tokopedia-ai.cs.ui.ac.id</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>web_research: https://cs.ui.ac.id/personnel/fariz-darari/ ; cross-checked via a second independently-worded WebSearch query returning the same fariz@ui.ac.id address consistently (per this session's WebFetch-egress-blocked fallback protocol) — Faculty lead at the Tokopedia-UI AI Center of Excellence, Indonesia's first AI development center, built around an NVIDIA DGX-1 deep-learning supercomputer hosted at Fasilkom UI -- a named, domain-matched (ui.ac.id) technical contact for a company already</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc179ddc13238</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:17+00:00</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>info@worldvueribyond.com</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>WorldVuer iByond (Quantum AI Data Center, Batam)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.worldvueribyond.com</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>web_research: https://bkpm.go.id/id/info/siaran-pers/ri-siap-fasilitasi-investasi-data-center-ai-pertama-di-asia-senilai-rp6-t ; cross-checked via https://kepri.antaranews.com/berita/228541/bkpm-fasilitasi-investasi-pusat-data-ai-pertama-di-asia-senilai-rp6-triliun-di-batam and a second independently-worded WebSearch query confirming info@worldvueribyond.com on the company's own worldvueribyond.com site (per WebFetch-egress-blocked fallback protocol) — BKPM-facilitated US$400M (~Rp6 trillion) jo</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17cb57f253f</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:29+00:00</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>msudarma@unud.ac.id</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Ir. Made Sudarma, MASc., IPU., ASEAN Eng.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Head, Udayana Center of Excellence for Artificial Intelligence (UCEAI)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Universitas Udayana</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://uceai.unud.ac.id</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>web_research: https://udayananetworking.unud.ac.id/lecturer/credential/3002-made-sudarma ; cross-checked via a second independently-worded WebSearch query returning the same msudarma@unud.ac.id address (per WebFetch-egress-blocked fallback protocol) — Heads UCEAI, Udayana's dedicated AI research center focused on AI development/application for Bali and Eastern Indonesia (same center already cited as the technology-need signal for the existing generic humas@unud.ac.id row) -- a named, domain-matc</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17b2788383b</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>sally.comollo@global.ntt</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sally Comollo</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Director of Communications, NTT Global Data Centers</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NTT Global Data Centers (Singapore)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://services.global.ntt</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>web_research: https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific/serangoon-data-center — NTT operates Serangoon Data Center (SG1) in Singapore, its first self-built/self-managed DC outside Japan, running an N+1 chilled-water cooling system; NTT Global Data Centers own AI-and-HPC-ready-data-centers page (services.global.ntt) describes actively deploying liquid cooling and direct-to-chip cold plates across its portfolio including Asia-Pacific</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17e133672d6</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:34+00:00</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -9378,7 +9378,11 @@
           <t>ITS</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.its.ac.id/katd/</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
@@ -9455,7 +9459,11 @@
           <t>JTC Corporation</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
@@ -9532,7 +9540,11 @@
           <t>Universitas Gadjah Mada</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://ugm.ac.id</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
@@ -9605,7 +9617,11 @@
           <t>Bridge Data Centres</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.bridgedatacentres.com</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
@@ -9682,7 +9698,11 @@
           <t>Empyrion Digital</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://empyriondigital.com</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U124"/>
+  <dimension ref="A1:U131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10078,6 +10078,553 @@
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>college_central@ite.edu.sg</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Institute of Technical Education (ITE) College Central - AiTE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.ite.edu.sg</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>web_research: https://thetechrevolutionist.com/2022/01/ite-and-nvidia-launch-ai-workforce-readiness-programme.html</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f59380c75d</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>humas@pajak.go.id</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Public Relations (Humas), Direktorat Jenderal Pajak</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) - Kementerian Keuangan RI</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.pajak.go.id</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>web_research: https://www.liputan6.com/tekno/read/8295162/bangun-coretax-hingga-pusat-data-ai-lg-cns-sabet-penghargaan-dari-djp-kemenkeu</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f3bd0a204d</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>info@smplus.com</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SM+ Data Centers (PT DSST Mas Gemilang / Sinar Mas)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://smplus.com</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>web_research: https://w.media/sm-data-centers-kira-and-lg-sinar-mas-top-out-smx01-in-jakarta/</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f35364a40f</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>media@singaporetech.edu.sg</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Technology (SIT)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.singaporetech.edu.sg</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>web_research: https://www.singaporetech.edu.sg/news/sit-marks-opening-its-flagship-ai-centre-sit-punggol-campus-key-initiatives-and-partnerships-advance</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f3eecdf3b7</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>nuhs_media@nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>National University Health System (NUHS)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>web_research: https://www.nuhs.edu.sg/about-nuhs/contact-us</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f44088ec51</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>pohseng@nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Assoc Prof Lee Poh Seng</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Programme Director, Sustainable Tropical Data Centre Testbed (STDCT); Head, Dept of Mechanical Engineering, NUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>National University of Singapore (NUS) - Sustainable Tropical Data Centre Testbed</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://cde.nus.edu.sg/me/staff/lee-poh-seng/</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>web_research: https://news.nus.edu.sg/worlds-first-tropical-climate-data-centre-testbed/</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f4a13d159b</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ygwen@ntu.edu.sg</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Prof Wen Yonggang</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Programme Co-Director, Sustainable Tropical Data Centre Testbed (STDCT); Professor, NTU</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University (NTU) - Sustainable Tropical Data Centre Testbed</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://personal.ntu.edu.sg/ygwen/</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>web_research: https://news.nus.edu.sg/worlds-first-tropical-climate-data-centre-testbed/</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f53f00af9b</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U131"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10625,6 +10625,642 @@
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>audrey.lau.l.p@singhealth.com.sg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Audrey Lau</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Group Chief Communications Officer</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SingHealth (Singapore General Hospital Campus)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.singhealth.com.sg</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>web_research: https://www.singhealth.com.sg/news/announcements/supercomputer-for-complex-health-research-at-new-centre</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>1a0d65fddfe6c101</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>help-occ@rp.edu.sg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Office of Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Republic Polytechnic (RP) - AI Technology Centre (AITC)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.rp.edu.sg</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>web_research: https://www.rp.edu.sg/about-us/contact-us/</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>1a0d65fe2e523eb5</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ir@digitalcorereit.com</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mabel Tan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Director, Capital Markets &amp; Investor Relations</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Digital Core REIT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.digitalcorereit.com</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>web_research: https://www.digitalcorereit.com/investor-relations/email-alerts-and-ir-contact/default.aspx</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>1a0d65fea7d8bcae</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ir@superx.sg</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SuperX AI Technology Limited</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.superx.sg</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/ai-compute-simplified-st-telemedia-global-data-centres-and-super-x-0cmut4phmwuj.html</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>1a0d65fefbbb0c20</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>marketing@bitera-dc.com</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tedy Harjanto</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Bitera Data Center (PT Mitra Informatika Gemilang)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.bitera-dc.com/</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/bitera-data-center-in-jakarta-indonesia-launches-operations/</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>1a0d65fca086c963</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>media@certisgroup.com</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Media Contact</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Certis Group</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.certisgroup.com</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>web_research: https://servers.asus.com/stories/Certis</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>1a0d65ff49a422a6</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>sales@dtp.net.id</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Michael Alifen</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Director &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DTP (PT Dwi Tunggal Putra)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.dtp.net.id/</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>web_research: https://www.dtp.net.id/en/data-center-services/data-center</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>1a0d65fd53ad6410</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>sales@mettadc.com</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sukoco Halim</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>President Director &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>MettaDC (PT MettaDC Teknologi Indonesia)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://mettadc.com/</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theiconomics.com/market-expansion/proyek-pertama-resmi-beroperasi-mettadc-akan-terus-bangun-data-center-hingga-500-mw/</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>1a0d65fd1d7dced6</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U139"/>
+  <dimension ref="A1:U144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11261,6 +11261,403 @@
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>info@inti.co.id</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PT INTI (Persero)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.inti.co.id</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>web_research: https://www.inti.co.id/?p=13158 — State-owned telecom manufacturer PT INTI (Persero) is developing an AI GPU-based Data Center on its 8-hectare Bandung headquarters site (3,888 sqm operational facility), per its own site news and a May 2024 MoU with PT Jagat Bali Lestari to build and operate the facility, corroborated by a second independent report (i-portal.inti.co.id/post/4379/bandung-punya-ai-data-center) confirming the AI GPU data center is being developed there.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4b636224a8</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>kee_yuan_ngiam@nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>A/Prof Ngiam Kee Yuan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Group Chief Technology Officer &amp; Head, AI Office, NUHS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NUHS</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>web_research: https://www.biospectrumasia.com/company-results/54/22939/singapores-nuhs-launches-first-ai-driven-supercomputer-to-empower-healthcare-projects.html ; contact confirmed via https://discovery.nuhs.edu.sg/2737-kee-yuan-ngiam and https://www.sgdi.gov.sg/ministries/moh/others/nuhs/departments/gito/Departments/aio — Leads NUHS's AI Office and the Prescience supercomputer initiative -- Singapore's third national supercomputer and first in healthcare, running multiple NVIDIA DGX A100 nodes for medical LLM training, built with NSCC -- a genuinely on-point named lead for the facility already cited as NUHS's technology-need signal</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4bc6a7e193</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>media@ovhcloud.com</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Marie Vaillaud</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Communications and PR Manager</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>OVHcloud Singapore</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.ovhcloud.com/en-sg/</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/ovhcloud-launches-data-center-in-singapore/ ; press contact confirmed via corporate.ovhcloud.com newsroom boilerplate — OVHcloud launched SGP2, its second Singapore data center, billed as its most sustainable APAC facility, expanding Bare Metal/dedicated server capacity to meet regional AI and cloud demand</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4c0d85fdf2</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>rickie.patani@nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Prof Rickie Patani</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Professor of Neuroscience &amp; Director, Neurobiology Programme, Life Sciences Institute, NUS Medicine</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NUS Medicine</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://medicine.nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>web_research: https://medicine.nus.edu.sg/news/nus-medicine-dayone-and-cortical-labs-unveil-biological-data-center-prototype-in-singapore/ ; contact confirmed via https://www.nus.edu.sg/lsi/principal-investigators-3/prof-rickie-patani/ — NUS Medicine, DayOne Data Centers and Cortical Labs unveiled a Biological Data Centre prototype in Singapore (Aug 2026) -- 20 CL1 biological-computing units powered by 16 million living human neurons, requiring precise thermal/environmental control per rack; Prof Patani supervises the neuron cultures used in the deployment as Director of NUS LSI's Neurobiology Programme</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4b9cc3375b</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>zhengkui.wang@singaporetech.edu.sg</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Daniel Zhengkui Wang</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Director, SIT x NVIDIA AI Centre (SNAIC) &amp; Associate Professor, Infocomm Technology Cluster</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Technology</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.singaporetech.edu.sg</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>web_research: https://www.singaporetech.edu.sg/news/sit-marks-opening-its-flagship-ai-centre-sit-punggol-campus-key-initiatives-and-partnerships-advance ; contact confirmed via https://www.singaporetech.edu.sg/directory/faculty/daniel-zhengkui-wang — Director of SIT's flagship SNAIC facility at Punggol Campus, a ~250 sqm AI centre built around an NVIDIA DGX H200 serving 50+ research engineers/students and 20+ industry partners -- a real, named lead for the same facility already cited as SIT's technology-need signal</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4ba7fdb5f0</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -9880,7 +9880,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -9891,17 +9891,17 @@
           <t>gmail:1a0cc17cb57f253f</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>4.4.1 The recipient server did not accept our requests to connect (timed out after 45h retry window); [worldvueribyond.com 2606:4700:3034::ac43:951d: timed out] [worldvueribyond.com 2606:4700:3032::6815:21c8: timed out] [worldvueribyond.com 172.67.149.29: timed out] [worldvueribyond.com 104.21.33.200: timed out]</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>2026-09-23T02:28:10+00:00</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:28:29+00:00</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U144"/>
+  <dimension ref="A1:U146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11658,6 +11658,160 @@
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>info@epsilontel.com</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Epsilon Telecommunications, a KT company</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://epsilontel.com</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>web_research: https://baxtel.com/data-center/epsilon-singapore-new-tech-park and https://www.datacenters.com/epsilon-telecommunications-singapore</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>1a0f025bf08c9490</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:29:50+00:00</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:30:05+00:00</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>suyi@a-star.edu.sg</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Dr Su Yi</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Executive Director, A*STAR Institute of Advanced Intelligence and Computing (IAIC)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>A*STAR Institute of Advanced Intelligence and Computing (IAIC)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/iaic</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>web_research: https://www.sgdi.gov.sg/ministries/mti/statutory-boards/a-star/departments/re/departments/iaic</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>1a0f025c1ccbb399</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:29:50+00:00</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:30:05+00:00</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U146"/>
+  <dimension ref="A1:U156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11812,6 +11812,796 @@
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>allocare@allobank.com</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Allo Bank Indonesia</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.allobank.com</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0822 0822 4110</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>080 4110 4110</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>web_research: https://tiaonline.org/942-datacenter/pt-allo-bank-indonesia-tbk-data-center-allo-bank/ ; contact confirmed via Allo Bank official verified account, e.g. https://x.com/AlloBankID/status/2011269529486442641 — Allo Bank separated its infrastructure from parent Bank Mega and launched its own dedicated, TIA Rated-3 certified data center in May 2024</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028608588884</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ap.ask@global.ntt</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NTT Indonesia (NTT Global Data Centers)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://services.global.ntt</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>+65 6991 2020</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>web_research: https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific/jakarta-2a-data-center ; contact confirmed via https://services.global.ntt/en-us/speak-to-our-experts and https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific — Jakarta 2 Annex (JKT2A), NTT's third Indonesia facility, delivers 12MW of IT load purpose-built for high-density deployments supporting racks up to 40kW, opening early 2026</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028ba720fbc3</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>callcenter@dukcapil.kemendagri.go.id</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Ditjen Dukcapil, Kemendagri (Data Center Ampera)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://dukcapil.kemendagri.go.id</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>08118005373</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1500537</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>web_research: https://nirmedia.co/dukcapil-hadapi-tantangan-2026-dengan-penguatan-digitalisasi-dan-integritas/ ; contact confirmed via Ditjen Dukcapil official verified account, e.g. https://x.com/dukcapil168/status/1691300522341617665 — Building a Tier 3 data center ('Data Center Ampera') at the IPDN campus on Jalan Ampera, Jakarta, as backbone infrastructure for national population-data digital services, alongside expanded biometric servers and storage capacity</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02878d0e9351</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>contactus@bankbsi.co.id</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>I Wayan Pulantara</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Innovation Department Head</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Bank Syariah Indonesia (BSI)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.bankbsi.co.id</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>081584114040</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>14040 / +62 21 80639999</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>web_research: https://teknologi.bisnis.com/read/20260617/84/1981304/bsi-bris-targetkan-infrastruktur-ai-gateway-rampung-tahun-ini ; contact confirmed via BSI verified official account, e.g. https://x.com/bankbsi_id/status/1669650245427544065 — Building an internal 'AI Gateway' computing infrastructure targeted for completion in 2026 to support internal AI applications and prevent shadow AI use, per AI Strategy &amp; Innovation Department Head I Wayan Pulantara at the Indonesia Ethical AI Summit (June 2026)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02839627f518</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>info@idc.co.id</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IDC Indonesia (PT Internetindo Data Centra Indonesia)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.idc.co.id</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>+62 21 526-9988</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>web_research: https://www.idc.co.id/ — Indonesia's first carrier-neutral data center operator, now operating 6 facilities across Jakarta, Batam, Bandung, Surabaya and Makassar carrying over 95% of Indonesian internet traffic — Indonesia's first carrier-neutral data center operator, now operating 6 facilities across Jakarta, Batam, Bandung, Surabaya and Makassar carrying over 95% of Indonesian internet traffic</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028bc989ed33</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>marketing@ag-it.com</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Astragraphia Information Technology (AGIT)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.ag-it.com</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>(021) 2924 1177</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>web_research: https://www.itworks.id/53011/lewat-anak-usaha-astra-graphia-berencana-perkuat-bisnis-data-center.html ; contact confirmed via https://www.ag-it.com/contact-us — Astra Graphia's IT subsidiary AGIT is expanding its data center business and partnering with HPE and Equinix to build AI-based private cloud infrastructure for the Indonesian market</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028a5a72f66f</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>marketing@nongsadigital.com</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Nongsa Digital Park (Citramas Group)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://nongsadigital.com</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>+62 778 7100 673</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>web_research: https://nongsadigital.com/dc-hub-ndp/8-data-centre-infrastructure-nongsa-digital-park ; contact confirmed via https://nongsadigital.com/contact-us/ — NDP1 facility at Nongsa Digital Park (Batam) is designed for high-density enterprise, cloud, and AI workloads, with planned IT capacity of 120MW, hosting multiple data center operators (BW Digital, DayOne, Golden Digital Gateway, Racks Central) on its own park infrastructure</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02876c4ba0c6</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>marketingicp@iconpln.co.id</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PLN Icon Plus (PT Indonesia Comnets Plus)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.plniconplus.co.id</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>web_research: https://listrikindonesia.com/detail/14093/energi-bersih-pln-icon-plus-siap-dukung-proyek-data-center-indonesia ; contact confirmed via the company's own site, https://lights.iconpln.co.id/article/37 (iconpln.co.id and plniconplus.co.id are the same company under its PLN Icon Plus rebrand, per https://iconews.iconpln.co.id/rebranding-pln-icon-plus-setting-tone-from-the-top/) — PLN Icon Plus (ICON+), PLN's telecom/data center subsidiary, states its commitment to supporting green data center development in Indonesia and operates its own DC2 data center facility amid rising AI-driven power and cooling demand</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028a241d929f</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>noc@napinfo.co.id</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Matrix NAP Info (PT NAP Info Lintas Nusa)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.napinfo.co.id</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1-500-787 / +62 21 3970 1787</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>web_research: https://napinfo.co.id/highlights/article/id/matrix-nap-info-jalin-kerja-sama-strategis-dengan-digital-realty-bersama-untuk-perkuat-ekosistem-infrastruktur-digital-nasional ; contact confirmed via https://www.napinfo.co.id/contact-us — Matrix NAP Info operates its own Matrix Data Center and struck a strategic partnership with Digital Realty Bersama to strengthen Jakarta data center interconnection for AI/cloud growth</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028620d291fb</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>support@lintasarta.co.id</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Lintasarta (PT Aplikanusa Lintasarta)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.lintasarta.net</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>08561114052</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>14052 / +62 21 80669499</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>web_research: https://freehire.me/jobs/cloud-data-center-engineer-gpu-openstack-lintasarta-qdsgh4bu and https://freehire.me/jobs/data-center-engineer-l2-lintasarta-qkksv7zy ; contact confirmed via https://www.lintasarta.net/en/contact-us/ — Actively hiring multiple onsite 24x7 Data Center Engineers (L1/L2/L3) for a large-scale GPU cloud built on rack-scale NVIDIA GB200 NVL72, with explicit responsibility for liquid-cooling systems (CDU and secondary loop) operation, monitoring and anomaly handling, alongside its NVIDIA-powered GPU Merdeka sovereign AI GPUaaS cloud already launched</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028365b6c54f</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U156"/>
+  <dimension ref="A1:U173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12602,6 +12602,1379 @@
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>christina.koh@sttelemediagdc.com</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Christina Koh</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Head, Group Marketing and Communications</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ST Telemedia Global Data Centres</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.sttelemediagdc.com</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>web_research: https://www.sttelemediagdc.com/newsroom/st-telemedia-global-data-centres-announces-new-executive-appointments — STT GDC operates multiple Singapore data centre campuses and is developing the FutureGrid HVDC-AI testbed; Christina Koh is named alongside Chow Yi as the company's own media contact across its newsroom press releases.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547310677735</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>contactus@synapxe.sg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Synapxe</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.synapxe.sg</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>web_research: https://www.synapxe.sg/healthtech/cloud/h-cloud — Synapxe, Singapore's national HealthTech agency, built H-Cloud to rationalise and consolidate local hospital data centres into a modernised, nation-wide private cloud serving all public hospitals, specialty centres, polyclinics and nursing homes.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472d8f8548c</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>corpcomms@ocbc.com</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Group Brand and Communications</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OCBC Bank</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.ocbc.com</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapores-ocbc-bank-to-introduce-rack-based-data-center-cooling/ — OCBC operates its own S$240M purpose-built data center in Singapore (first purpose-built DC owned by a Singapore bank) and is implementing a rack-based cooling system to cut emissions by 400+ tons/year; separately hiring a Data Centre Facilities Engineer and a Lead, Data Centre Facilities Management (AVP/VP) for the Loyang facility.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5471f98cfb7a</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>investor.relations@keppeldcreit.com</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Keppel DC REIT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.keppeldcreit.com</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>web_research: https://www.keppeldcreit.com/en/investor-relations/ir-contact/ — Keppel DC REIT is participating in the Keppel DC Singapore 9 build at the AI-ready Genting Lane campus (construction start mid-2026, 19MW), alongside Keppel Data Centre Funds II and III.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54728c833da5</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ir_industrial@mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Cheng Mui Lian</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Investor Relations and Sustainability</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Mapletree Industrial Trust</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.mapletreeindustrialtrust.com</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>web_research: https://www.mapletreeindustrialtrust.com/about-us/ — Mapletree Industrial Trust's data-centre portfolio is roughly 57% of its S$8.3B total AUM, including the purpose-built 7 Tai Seng Drive facility (fully leased to Equinix Singapore) and the Sunview Drive data centre in Singapore, plus 13 data centres held via JV with Mapletree Investments in North America.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54724a989642</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>lauren.crystal@smc.co</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Lauren Crystal</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Head of Communications</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sustainable Metal Cloud (SMC)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://smc.co</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapores-sustainable-metal-cloud-outlines-global-expansion-plans/ — Singapore-founded and HQ'd SMC runs fully immersion-cooled NVIDIA GPU clusters (SIN01/SIN02 availability zones at STT GDC) for AI training/inference, achieving a PUE of 1.03 via its HyperCube immersion-cooling technology.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472318d99a1</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>luana.low@gf.com</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Luana Low</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Deputy Director, Corporate Communications (Public Relations, Singapore)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>GlobalFoundries Singapore</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://gf.com</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edb.gov.sg/en/about-edb/media-releases-publications/globalfoundries-opens-us4-billion-expansion-facility-in-singapore.html — GlobalFoundries officially opened a US$4B expansion fab in Singapore (23,000 sqm), its most advanced Singapore semiconductor facility to date, raising overall Singapore capacity to ~1.5M 300mm wafers/year.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547267649121</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>nola.pocock@colt.net</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nola Pocock</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VP, Global Communications (Colt Group)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Colt Data Centre Services Singapore</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.coltdatacentres.net</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>web_research: https://www.colt.net/resources/insights/connectivity-for-mc-digital-realty-data-centre — Colt operates a Singapore data center at 29A International Business Park Road; Colt Group's own Global Communications lead (covering both Colt Technology Services and Colt Data Centre Services announcements) is Nola Pocock, consistently listed as press contact on colt.net data-centre-related releases.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472e0be35ce</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>tanya.netto@oracle.com</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tanya Netto</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Communications &amp; PR Lead, ASEAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Infrastructure Singapore</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/sg/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>web_research: https://blogs.oracle.com/cloud-infrastructure/oracle-opens-second-cloud-region-in-singapore — Oracle opened a second Oracle Cloud Region in Singapore to meet rapidly growing AI/cloud demand, enabling customers to migrate mission-critical AI workloads.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472bfb7b7c4</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ai.center@binus.edu</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Prof. Bens Pardamean</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Director, Artificial Intelligence R&amp;D Center (AIRDC)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BINUS University (AI R&amp;D Center)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://research.binus.ac.id/airdc/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>+62.21 530 0244</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>web_research: https://research.binus.ac.id/airdc/ ; https://binus.ac.id/2019/04/binus-dirikan-pusat-riset-artificial-intelligence/ — BINUS University AI R&amp;D Center (AIRDC), founded via NVIDIA-BINUS collaboration, operates a GPU cluster for AI research and industry collaboration, directed by Prof. Bens Pardamean</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475eb87633c</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>corsec@pancaanugrahwisesa.com</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Corporate Secretary</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PT NexAI Digital Infrastruktur Tbk (MGLV, formerly PT Panca Anugrah Wisesa Tbk)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>http://pancaanugrahwisesa.com</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>+62 21 718 0349</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>web_research: https://harianenergi.com/detail/1440376/dapat-restu-rupslb-nexai-mantap-garap-bisnis-ai-data-center ; https://bisnisinsight.com/detail/921750/nexai-mglv-resmi-masuk-bisnis-ai-data-center-usai-restu-rupslb — IDX-listed PT NexAI Digital Infrastruktur Tbk (MGLV) received shareholder approval (RUPSLB, July 2026) to formally pivot its core business from furniture/household equipment to AI-based data center infrastructure</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475ddf337f9</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>info@edgnex.com</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DAMAC Digital (EDGNEX Cikarang AI Campus)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.edgnex.com</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>+971 4 373 2 373</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgnex.com/contact/ ; https://www.idnfinancials.com/news/56071/dubais-damac-digital-to-build-usd-2-3-billion-data-centre-in-cikarang — DAMAC Digital (EDGNEX) is building a $2.3B AI data center in Greenland International Industrial Center, Pasirranji, Bekasi (JKT02/Cikarang AI Campus), designed for high-density AI racks with a projected capacity exceeding 144MW, first phase slated for Q3 2026 completion</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54759960550c</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>infodgx@gunadarma.ac.id</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Detty Purnamasari</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Head, AI and Robotics Development Team (DGX Development Team)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Universitas Gunadarma</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.hpc-hub.gunadarma.ac.id</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>+628-1212-9955-61</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>web_research: https://www.praktikum-hpc.gunadarma.ac.id/kontak/tim-pengembangan-dgx ; https://www.hpc-hub.gunadarma.ac.id/kontak — Prof. Dr. Detty Purnamasari heads the DGX Development Team overseeing Gunadarma University NVIDIA DGX-1 and DGX A100 supercomputers at its dedicated HPC/DGX hub for AI and data-intensive research</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54761cbada73</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>inquiry@indokeppeldc.com</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>IndoData Data Center (Salim Group, formerly IndoKeppel Data Centres)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://indokeppeldc.com</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>+622139520140</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/keppel-salim-group-launch-data-center-in-bogor-indonesia/ ; https://w.media/indokeppel-sees-significant-data-center-opportunities-in-indonesia/ — IndoKeppel Data Centre 1 (IKDC1) in Bogor, a Salim Group/Keppel JV (Salim Group took full ownership in Dec 2025 and relaunched as IndoData Data Center), is a 7-hectare campus planned for 50MW+ of IT power across 3 phases, featuring N+1 water-cooled chillers and dual water supply, with a stated strategic focus on AI and hyperscale computing; IndoData has up to 500MW of power capacity secured under contract with PLN</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475268bea7a</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>inquiry@lgsinarmas.com</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LG Sinar Mas Technology Solutions (LG CNS / SM+ JV)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.lgsinarmas.com</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>+62-21-31990258</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>web_research: https://www.sinarmas.com/blog/?p=4168 ; https://www.lgsinarmas.com/ — LG Sinar Mas, a joint venture between South Korean DC services provider LG CNS and Sinar Mas-backed PT SMPlus Digital Investment (SM+), is developing a US$300M AI-based data center on a 44,195 sqm facility in Menteng Atas, Setiabudi, Jakarta, scheduled to begin operations in H2 2026</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54756301e30b</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>sales@dhs-dc.com</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Stanley Go</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Digital Hyperspace Indonesia (DHI)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://dh-indonesia.com</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>web_research: https://dh-indonesia.com/contact/ ; https://dh-indonesia.com/about/ — PT Digital Hyperspace Indonesia operates DHI, a Tier III hyperscale data center in Pasirranji, Central Cikarang, Bekasi Regency, West Java, with an initial 20MW IT load (1,200,000 SF purpose-built facility), financed by the GTC Fund and co-investors; Operations Manager Stanley Go is ASHRAE BCxP-certified</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547554b25881</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>selena.sheikh@princetondg.com</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Selena Sheikh</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Corporate Communications Associate Director, Public Relations</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Princeton Digital Group (PDG) Indonesia</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://princetondg.com</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>web_research: https://princetondg.com/newsroom/princeton-digital-group-launches-its-22mw-hyperscale-data-center-in-greater-jakarta-2/ — PDG operates JC1 (6MW) and JC2 (22MW hyperscale, launched) data centers in Cibitung, Greater Jakarta, and agreed to acquire a 70%% stake in XL Axiata Indonesian data centers (5 sites) with US$100M growth capital committed to expand capacity</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475a8ba596c</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database.xlsx
+++ b/data/crm_database.xlsx
@@ -13777,7 +13777,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -13788,17 +13788,17 @@
           <t>gmail:1a0f54756301e30b</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>550 5.4.1 Recipient address rejected: Access denied. (lgsinarmas-com.mail.protection.outlook.com)</t>
+        </is>
+      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>2026-10-01T02:24:30+00:00</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>2026-10-01T02:24:57+00:00</t>
-        </is>
-      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
           <t>none</t>
